--- a/config/xlsx/home_meridians.xlsx
+++ b/config/xlsx/home_meridians.xlsx
@@ -491,10 +491,8 @@
       <c r="D2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":6},{"token":3,"amount":50}],"items":[{"id":12001,"count":1}]}</t>
-        </is>
+      <c r="E2" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":6},{"token":3,"amount":50}],"items":[{"id":12001,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="3">
@@ -512,10 +510,8 @@
       <c r="D3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":6},{"token":3,"amount":50},{"token":1,"amount":10}],"items":[{"id":16001,"count":1},{"id":17001,"count":1}]}</t>
-        </is>
+      <c r="E3" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":6},{"token":3,"amount":50},{"token":1,"amount":10}],"items":[{"id":16001,"count":1},{"id":17001,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="4">
@@ -533,10 +529,8 @@
       <c r="D4" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":16},{"token":3,"amount":33}],"items":[{"id":15002,"count":1},{"id":11002,"count":1}]}</t>
-        </is>
+      <c r="E4" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":16},{"token":3,"amount":33}],"items":[{"id":15002,"count":1},{"id":11002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="5">
@@ -554,10 +548,8 @@
       <c r="D5" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":16},{"token":3,"amount":34}],"items":[{"id":13002,"count":1},{"id":12002,"count":1}]}</t>
-        </is>
+      <c r="E5" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":16},{"token":3,"amount":34}],"items":[{"id":13002,"count":1},{"id":12002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="6">
@@ -575,10 +567,8 @@
       <c r="D6" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":16},{"token":3,"amount":33}],"items":[{"id":18002,"count":1},{"id":17002,"count":1}]}</t>
-        </is>
+      <c r="E6" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":16},{"token":3,"amount":33}],"items":[{"id":18002,"count":1},{"id":17002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="7">
@@ -596,10 +586,8 @@
       <c r="D7" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":20},{"token":3,"amount":25}],"items":[{"id":15002,"count":1},{"id":11002,"count":1}]}</t>
-        </is>
+      <c r="E7" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":20},{"token":3,"amount":25}],"items":[{"id":15002,"count":1},{"id":11002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="8">
@@ -617,10 +605,8 @@
       <c r="D8" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":20},{"token":3,"amount":25}],"items":[{"id":13002,"count":1},{"id":12002,"count":1}]}</t>
-        </is>
+      <c r="E8" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":20},{"token":3,"amount":25}],"items":[{"id":13002,"count":1},{"id":12002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="9">
@@ -638,10 +624,8 @@
       <c r="D9" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":20},{"token":3,"amount":25}],"items":[{"id":18002,"count":1},{"id":17002,"count":1}]}</t>
-        </is>
+      <c r="E9" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":20},{"token":3,"amount":25}],"items":[{"id":18002,"count":1},{"id":17002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="10">
@@ -659,10 +643,8 @@
       <c r="D10" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":20},{"token":3,"amount":25}],"items":[{"id":15002,"count":1},{"id":11002,"count":1}]}</t>
-        </is>
+      <c r="E10" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":20},{"token":3,"amount":25}],"items":[{"id":15002,"count":1},{"id":11002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="11">
@@ -680,10 +662,8 @@
       <c r="D11" s="3" t="n">
         <v>262</v>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":20}],"items":[{"id":15002,"count":1},{"id":11002,"count":1}]}</t>
-        </is>
+      <c r="E11" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":20}],"items":[{"id":15002,"count":1},{"id":11002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="12">
@@ -701,10 +681,8 @@
       <c r="D12" s="3" t="n">
         <v>262</v>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":20}],"items":[{"id":13002,"count":1},{"id":12002,"count":1}]}</t>
-        </is>
+      <c r="E12" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":20}],"items":[{"id":13002,"count":1},{"id":12002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="13">
@@ -722,10 +700,8 @@
       <c r="D13" s="3" t="n">
         <v>262</v>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":20},{"token":3,"amount":20}],"items":[{"id":18002,"count":1},{"id":17002,"count":1}]}</t>
-        </is>
+      <c r="E13" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":20},{"token":3,"amount":20}],"items":[{"id":18002,"count":1},{"id":17002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="14">
@@ -743,10 +719,8 @@
       <c r="D14" s="3" t="n">
         <v>262</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":20}],"items":[{"id":15002,"count":1},{"id":11002,"count":1}]}</t>
-        </is>
+      <c r="E14" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":20}],"items":[{"id":15002,"count":1},{"id":11002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="15">
@@ -764,10 +738,8 @@
       <c r="D15" s="3" t="n">
         <v>262</v>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":20}],"items":[{"id":13002,"count":1},{"id":12002,"count":1}]}</t>
-        </is>
+      <c r="E15" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":20}],"items":[{"id":13002,"count":1},{"id":12002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="16">
@@ -785,10 +757,8 @@
       <c r="D16" s="3" t="n">
         <v>315</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":17}],"items":[{"id":15002,"count":1},{"id":11002,"count":1}]}</t>
-        </is>
+      <c r="E16" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":17}],"items":[{"id":15002,"count":1},{"id":11002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="17">
@@ -806,10 +776,8 @@
       <c r="D17" s="3" t="n">
         <v>315</v>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":22},{"token":3,"amount":16}],"items":[{"id":13002,"count":1},{"id":12002,"count":1}]}</t>
-        </is>
+      <c r="E17" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":22},{"token":3,"amount":16}],"items":[{"id":13002,"count":1},{"id":12002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="18">
@@ -827,10 +795,8 @@
       <c r="D18" s="3" t="n">
         <v>315</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":17}],"items":[{"id":18002,"count":1},{"id":17002,"count":1}]}</t>
-        </is>
+      <c r="E18" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":17}],"items":[{"id":18002,"count":1},{"id":17002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="19">
@@ -848,10 +814,8 @@
       <c r="D19" s="3" t="n">
         <v>315</v>
       </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":17}],"items":[{"id":15002,"count":1},{"id":11002,"count":1}]}</t>
-        </is>
+      <c r="E19" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":17}],"items":[{"id":15002,"count":1},{"id":11002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="20">
@@ -869,10 +833,8 @@
       <c r="D20" s="3" t="n">
         <v>315</v>
       </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":22},{"token":3,"amount":16}],"items":[{"id":13002,"count":1},{"id":12002,"count":1}]}</t>
-        </is>
+      <c r="E20" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":22},{"token":3,"amount":16}],"items":[{"id":13002,"count":1},{"id":12002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="21">
@@ -890,10 +852,8 @@
       <c r="D21" s="3" t="n">
         <v>315</v>
       </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":17}],"items":[{"id":18002,"count":1},{"id":17002,"count":1}]}</t>
-        </is>
+      <c r="E21" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":21},{"token":3,"amount":17}],"items":[{"id":18002,"count":1},{"id":17002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="22">
@@ -911,10 +871,8 @@
       <c r="D22" s="3" t="n">
         <v>377</v>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":14}],"items":[{"id":15002,"count":1},{"id":11002,"count":1}]}</t>
-        </is>
+      <c r="E22" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":14}],"items":[{"id":15002,"count":1},{"id":11002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="23">
@@ -932,10 +890,8 @@
       <c r="D23" s="3" t="n">
         <v>377</v>
       </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":32},{"token":3,"amount":15}],"items":[{"id":13002,"count":1},{"id":12002,"count":1}]}</t>
-        </is>
+      <c r="E23" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":32},{"token":3,"amount":15}],"items":[{"id":13002,"count":1},{"id":12002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="24">
@@ -953,10 +909,8 @@
       <c r="D24" s="3" t="n">
         <v>377</v>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":14}],"items":[{"id":18002,"count":1},{"id":17002,"count":1}]}</t>
-        </is>
+      <c r="E24" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":14}],"items":[{"id":18002,"count":1},{"id":17002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="25">
@@ -974,10 +928,8 @@
       <c r="D25" s="3" t="n">
         <v>377</v>
       </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":32},{"token":3,"amount":14}],"items":[{"id":15003,"count":1},{"id":11003,"count":1}]}</t>
-        </is>
+      <c r="E25" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":32},{"token":3,"amount":14}],"items":[{"id":15003,"count":1},{"id":11003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="26">
@@ -995,10 +947,8 @@
       <c r="D26" s="3" t="n">
         <v>377</v>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":14}],"items":[{"id":13003,"count":1},{"id":12003,"count":1}]}</t>
-        </is>
+      <c r="E26" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":14}],"items":[{"id":13003,"count":1},{"id":12003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="27">
@@ -1016,10 +966,8 @@
       <c r="D27" s="3" t="n">
         <v>377</v>
       </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":32},{"token":3,"amount":15}],"items":[{"id":18003,"count":1},{"id":17003,"count":1}]}</t>
-        </is>
+      <c r="E27" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":32},{"token":3,"amount":15}],"items":[{"id":18003,"count":1},{"id":17003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="28">
@@ -1037,10 +985,8 @@
       <c r="D28" s="3" t="n">
         <v>377</v>
       </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":14}],"items":[{"id":15003,"count":1},{"id":11003,"count":1}]}</t>
-        </is>
+      <c r="E28" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":14}],"items":[{"id":15003,"count":1},{"id":11003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="29">
@@ -1058,10 +1004,8 @@
       <c r="D29" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":12}],"items":[{"id":15003,"count":1},{"id":11003,"count":1}]}</t>
-        </is>
+      <c r="E29" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":12}],"items":[{"id":15003,"count":1},{"id":11003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="30">
@@ -1079,10 +1023,8 @@
       <c r="D30" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":13}],"items":[{"id":13003,"count":1},{"id":12003,"count":1}]}</t>
-        </is>
+      <c r="E30" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":13}],"items":[{"id":13003,"count":1},{"id":12003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="31">
@@ -1100,10 +1042,8 @@
       <c r="D31" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":12}],"items":[{"id":18003,"count":1},{"id":17003,"count":1}]}</t>
-        </is>
+      <c r="E31" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":12}],"items":[{"id":18003,"count":1},{"id":17003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="32">
@@ -1121,10 +1061,8 @@
       <c r="D32" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":13}],"items":[{"id":15003,"count":1},{"id":11003,"count":1}]}</t>
-        </is>
+      <c r="E32" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":13}],"items":[{"id":15003,"count":1},{"id":11003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="33">
@@ -1142,10 +1080,8 @@
       <c r="D33" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":12}],"items":[{"id":13003,"count":1},{"id":12003,"count":1}]}</t>
-        </is>
+      <c r="E33" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":12}],"items":[{"id":13003,"count":1},{"id":12003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="34">
@@ -1163,10 +1099,8 @@
       <c r="D34" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":13}],"items":[{"id":18003,"count":1},{"id":17003,"count":1}]}</t>
-        </is>
+      <c r="E34" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":13}],"items":[{"id":18003,"count":1},{"id":17003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="35">
@@ -1184,10 +1118,8 @@
       <c r="D35" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":12}],"items":[{"id":15003,"count":1},{"id":11003,"count":1}]}</t>
-        </is>
+      <c r="E35" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":12}],"items":[{"id":15003,"count":1},{"id":11003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="36">
@@ -1205,10 +1137,8 @@
       <c r="D36" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":13}],"items":[{"id":13003,"count":1},{"id":12003,"count":1}]}</t>
-        </is>
+      <c r="E36" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":13}],"items":[{"id":13003,"count":1},{"id":12003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="37">
@@ -1226,10 +1156,8 @@
       <c r="D37" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":11}],"items":[{"id":15003,"count":1},{"id":11003,"count":1}]}</t>
-        </is>
+      <c r="E37" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":11}],"items":[{"id":15003,"count":1},{"id":11003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="38">
@@ -1247,10 +1175,8 @@
       <c r="D38" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":34},{"token":3,"amount":11}],"items":[{"id":13003,"count":1},{"id":12003,"count":1}]}</t>
-        </is>
+      <c r="E38" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":34},{"token":3,"amount":11}],"items":[{"id":13003,"count":1},{"id":12003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="39">
@@ -1268,10 +1194,8 @@
       <c r="D39" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":11}],"items":[{"id":18003,"count":1},{"id":17003,"count":1}]}</t>
-        </is>
+      <c r="E39" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":11}],"items":[{"id":18003,"count":1},{"id":17003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="40">
@@ -1289,10 +1213,8 @@
       <c r="D40" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":11}],"items":[{"id":15003,"count":1},{"id":11003,"count":1}]}</t>
-        </is>
+      <c r="E40" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":11}],"items":[{"id":15003,"count":1},{"id":11003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="41">
@@ -1310,10 +1232,8 @@
       <c r="D41" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":34},{"token":3,"amount":12}],"items":[{"id":13003,"count":1},{"id":12003,"count":1}]}</t>
-        </is>
+      <c r="E41" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":34},{"token":3,"amount":12}],"items":[{"id":13003,"count":1},{"id":12003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="42">
@@ -1331,10 +1251,8 @@
       <c r="D42" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":11}],"items":[{"id":18003,"count":1},{"id":17003,"count":1}]}</t>
-        </is>
+      <c r="E42" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":11}],"items":[{"id":18003,"count":1},{"id":17003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="43">
@@ -1352,10 +1270,8 @@
       <c r="D43" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":11}],"items":[{"id":15003,"count":1},{"id":11003,"count":1}]}</t>
-        </is>
+      <c r="E43" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":11}],"items":[{"id":15003,"count":1},{"id":11003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="44">
@@ -1373,10 +1289,8 @@
       <c r="D44" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":34},{"token":3,"amount":11}],"items":[{"id":13003,"count":1},{"id":12003,"count":1}]}</t>
-        </is>
+      <c r="E44" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":34},{"token":3,"amount":11}],"items":[{"id":13003,"count":1},{"id":12003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="45">
@@ -1394,10 +1308,8 @@
       <c r="D45" s="3" t="n">
         <v>440</v>
       </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":11}],"items":[{"id":18003,"count":1},{"id":17003,"count":1}]}</t>
-        </is>
+      <c r="E45" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":33},{"token":3,"amount":11}],"items":[{"id":18003,"count":1},{"id":17003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="46">
@@ -1415,10 +1327,8 @@
       <c r="D46" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":15004,"count":1},{"id":11004,"count":1}]}</t>
-        </is>
+      <c r="E46" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":15004,"count":1},{"id":11004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="47">
@@ -1436,10 +1346,8 @@
       <c r="D47" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":13004,"count":1},{"id":12004,"count":1}]}</t>
-        </is>
+      <c r="E47" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":13004,"count":1},{"id":12004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="48">
@@ -1457,10 +1365,8 @@
       <c r="D48" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":34},{"token":3,"amount":10}],"items":[{"id":18004,"count":1},{"id":17004,"count":1}]}</t>
-        </is>
+      <c r="E48" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":34},{"token":3,"amount":10}],"items":[{"id":18004,"count":1},{"id":17004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="49">
@@ -1478,10 +1384,8 @@
       <c r="D49" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":15004,"count":1},{"id":11004,"count":1}]}</t>
-        </is>
+      <c r="E49" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":15004,"count":1},{"id":11004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="50">
@@ -1499,10 +1403,8 @@
       <c r="D50" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":13004,"count":1},{"id":12004,"count":1}]}</t>
-        </is>
+      <c r="E50" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":13004,"count":1},{"id":12004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="51">
@@ -1520,10 +1422,8 @@
       <c r="D51" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":18004,"count":1},{"id":17004,"count":1}]}</t>
-        </is>
+      <c r="E51" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":18004,"count":1},{"id":17004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="52">
@@ -1541,10 +1441,8 @@
       <c r="D52" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":15004,"count":1},{"id":11004,"count":1}]}</t>
-        </is>
+      <c r="E52" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":15004,"count":1},{"id":11004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="53">
@@ -1562,10 +1460,8 @@
       <c r="D53" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":34},{"token":3,"amount":10}],"items":[{"id":13004,"count":1},{"id":12004,"count":1}]}</t>
-        </is>
+      <c r="E53" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":34},{"token":3,"amount":10}],"items":[{"id":13004,"count":1},{"id":12004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="54">
@@ -1583,10 +1479,8 @@
       <c r="D54" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":18004,"count":1},{"id":17004,"count":1}]}</t>
-        </is>
+      <c r="E54" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":18004,"count":1},{"id":17004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="55">
@@ -1604,10 +1498,8 @@
       <c r="D55" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":15004,"count":1},{"id":11004,"count":1}]}</t>
-        </is>
+      <c r="E55" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":10}],"items":[{"id":15004,"count":1},{"id":11004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="56">
@@ -1625,10 +1517,8 @@
       <c r="D56" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":15004,"count":1},{"id":11004,"count":1}]}</t>
-        </is>
+      <c r="E56" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":15004,"count":1},{"id":11004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="57">
@@ -1646,10 +1536,8 @@
       <c r="D57" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":13004,"count":1},{"id":12004,"count":1}]}</t>
-        </is>
+      <c r="E57" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":13004,"count":1},{"id":12004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="58">
@@ -1667,10 +1555,8 @@
       <c r="D58" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":18004,"count":1},{"id":17004,"count":1}]}</t>
-        </is>
+      <c r="E58" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":18004,"count":1},{"id":17004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="59">
@@ -1688,10 +1574,8 @@
       <c r="D59" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":15004,"count":1},{"id":11004,"count":1}]}</t>
-        </is>
+      <c r="E59" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":15004,"count":1},{"id":11004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="60">
@@ -1709,10 +1593,8 @@
       <c r="D60" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":13004,"count":1},{"id":12004,"count":1}]}</t>
-        </is>
+      <c r="E60" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":13004,"count":1},{"id":12004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="61">
@@ -1730,10 +1612,8 @@
       <c r="D61" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":34},{"token":3,"amount":10}],"items":[{"id":18004,"count":1},{"id":17004,"count":1}]}</t>
-        </is>
+      <c r="E61" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":34},{"token":3,"amount":10}],"items":[{"id":18004,"count":1},{"id":17004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="62">
@@ -1751,10 +1631,8 @@
       <c r="D62" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":15004,"count":1},{"id":11004,"count":1}]}</t>
-        </is>
+      <c r="E62" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":15004,"count":1},{"id":11004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="63">
@@ -1772,10 +1650,8 @@
       <c r="D63" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":13004,"count":1},{"id":12004,"count":1}]}</t>
-        </is>
+      <c r="E63" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":13004,"count":1},{"id":12004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="64">
@@ -1793,10 +1669,8 @@
       <c r="D64" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":18004,"count":1},{"id":17004,"count":1}]}</t>
-        </is>
+      <c r="E64" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":18004,"count":1},{"id":17004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="65">
@@ -1814,10 +1688,8 @@
       <c r="D65" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":15004,"count":1},{"id":11004,"count":1}]}</t>
-        </is>
+      <c r="E65" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":15004,"count":1},{"id":11004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="66">
@@ -1835,10 +1707,8 @@
       <c r="D66" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":13004,"count":1},{"id":12004,"count":1}]}</t>
-        </is>
+      <c r="E66" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":35},{"token":3,"amount":9}],"items":[{"id":13004,"count":1},{"id":12004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="67">
@@ -1856,10 +1726,8 @@
       <c r="D67" s="3" t="n">
         <v>10158</v>
       </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":14001,"count":1},{"id":11005,"count":1}]}</t>
-        </is>
+      <c r="E67" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":14001,"count":1},{"id":11005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="68">
@@ -1877,10 +1745,8 @@
       <c r="D68" s="3" t="n">
         <v>10158</v>
       </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":21001,"count":1},{"id":12005,"count":1}]}</t>
-        </is>
+      <c r="E68" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":21001,"count":1},{"id":12005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="69">
@@ -1898,10 +1764,8 @@
       <c r="D69" s="3" t="n">
         <v>11081</v>
       </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":13005,"count":1},{"id":15005,"count":1}]}</t>
-        </is>
+      <c r="E69" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":13005,"count":1},{"id":15005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="70">
@@ -1919,10 +1783,8 @@
       <c r="D70" s="3" t="n">
         <v>10158</v>
       </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":28}],"items":[{"id":17005,"count":1},{"id":18005,"count":1}]}</t>
-        </is>
+      <c r="E70" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":28}],"items":[{"id":17005,"count":1},{"id":18005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="71">
@@ -1940,10 +1802,8 @@
       <c r="D71" s="3" t="n">
         <v>10158</v>
       </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":14001,"count":1},{"id":11005,"count":1}]}</t>
-        </is>
+      <c r="E71" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":14001,"count":1},{"id":11005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="72">
@@ -1961,10 +1821,8 @@
       <c r="D72" s="3" t="n">
         <v>10158</v>
       </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":21001,"count":1},{"id":12005,"count":1}]}</t>
-        </is>
+      <c r="E72" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":21001,"count":1},{"id":12005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="73">
@@ -1982,10 +1840,8 @@
       <c r="D73" s="3" t="n">
         <v>9376</v>
       </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":13005,"count":1},{"id":15005,"count":1}]}</t>
-        </is>
+      <c r="E73" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":13005,"count":1},{"id":15005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="74">
@@ -2003,10 +1859,8 @@
       <c r="D74" s="3" t="n">
         <v>10158</v>
       </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":17005,"count":1},{"id":18005,"count":1}]}</t>
-        </is>
+      <c r="E74" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":17005,"count":1},{"id":18005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="75">
@@ -2024,10 +1878,8 @@
       <c r="D75" s="3" t="n">
         <v>10158</v>
       </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":14001,"count":1},{"id":11005,"count":1}]}</t>
-        </is>
+      <c r="E75" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":14001,"count":1},{"id":11005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="76">
@@ -2045,10 +1897,8 @@
       <c r="D76" s="3" t="n">
         <v>9376</v>
       </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":21001,"count":1},{"id":12005,"count":1}]}</t>
-        </is>
+      <c r="E76" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":21001,"count":1},{"id":12005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="77">
@@ -2066,10 +1916,8 @@
       <c r="D77" s="3" t="n">
         <v>9376</v>
       </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":28}],"items":[{"id":13005,"count":1},{"id":15005,"count":1}]}</t>
-        </is>
+      <c r="E77" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":28}],"items":[{"id":13005,"count":1},{"id":15005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="78">
@@ -2087,10 +1935,8 @@
       <c r="D78" s="3" t="n">
         <v>10158</v>
       </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":17005,"count":1},{"id":18005,"count":1}]}</t>
-        </is>
+      <c r="E78" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":17005,"count":1},{"id":18005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="79">
@@ -2108,10 +1954,8 @@
       <c r="D79" s="3" t="n">
         <v>9376</v>
       </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":14001,"count":1},{"id":11005,"count":1}]}</t>
-        </is>
+      <c r="E79" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":14001,"count":1},{"id":11005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="80">
@@ -2129,10 +1973,8 @@
       <c r="D80" s="3" t="n">
         <v>9376</v>
       </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":21002,"count":1},{"id":12005,"count":1}]}</t>
-        </is>
+      <c r="E80" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":21002,"count":1},{"id":12005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="81">
@@ -2150,10 +1992,8 @@
       <c r="D81" s="3" t="n">
         <v>9376</v>
       </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":13005,"count":1},{"id":15005,"count":1}]}</t>
-        </is>
+      <c r="E81" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":13005,"count":1},{"id":15005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="82">
@@ -2171,10 +2011,8 @@
       <c r="D82" s="3" t="n">
         <v>12189</v>
       </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":17005,"count":1},{"id":18005,"count":1}]}</t>
-        </is>
+      <c r="E82" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":17005,"count":1},{"id":18005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="83">
@@ -2192,10 +2030,8 @@
       <c r="D83" s="3" t="n">
         <v>12189</v>
       </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":14002,"count":1},{"id":11005,"count":1}]}</t>
-        </is>
+      <c r="E83" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":14002,"count":1},{"id":11005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="84">
@@ -2213,10 +2049,8 @@
       <c r="D84" s="3" t="n">
         <v>12189</v>
       </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":28}],"items":[{"id":21002,"count":1},{"id":12005,"count":1}]}</t>
-        </is>
+      <c r="E84" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":28}],"items":[{"id":21002,"count":1},{"id":12005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="85">
@@ -2234,10 +2068,8 @@
       <c r="D85" s="3" t="n">
         <v>12189</v>
       </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":13005,"count":1},{"id":15005,"count":1}]}</t>
-        </is>
+      <c r="E85" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":13005,"count":1},{"id":15005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="86">
@@ -2255,10 +2087,8 @@
       <c r="D86" s="3" t="n">
         <v>11081</v>
       </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":17005,"count":1},{"id":18005,"count":1}]}</t>
-        </is>
+      <c r="E86" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":17005,"count":1},{"id":18005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="87">
@@ -2276,10 +2106,8 @@
       <c r="D87" s="3" t="n">
         <v>12189</v>
       </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":14002,"count":1},{"id":11005,"count":1}]}</t>
-        </is>
+      <c r="E87" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":14002,"count":1},{"id":11005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="88">
@@ -2297,10 +2125,8 @@
       <c r="D88" s="3" t="n">
         <v>12189</v>
       </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":21002,"count":1},{"id":12005,"count":1}]}</t>
-        </is>
+      <c r="E88" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":21002,"count":1},{"id":12005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="89">
@@ -2318,10 +2144,8 @@
       <c r="D89" s="3" t="n">
         <v>12189</v>
       </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":13005,"count":1},{"id":15005,"count":1}]}</t>
-        </is>
+      <c r="E89" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":13005,"count":1},{"id":15005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="90">
@@ -2339,10 +2163,8 @@
       <c r="D90" s="3" t="n">
         <v>11081</v>
       </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":17005,"count":1},{"id":18005,"count":1}]}</t>
-        </is>
+      <c r="E90" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":17005,"count":1},{"id":18005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="91">
@@ -2360,10 +2182,8 @@
       <c r="D91" s="3" t="n">
         <v>11081</v>
       </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":28}],"items":[{"id":14002,"count":1},{"id":11005,"count":1}]}</t>
-        </is>
+      <c r="E91" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":28}],"items":[{"id":14002,"count":1},{"id":11005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="92">
@@ -2381,10 +2201,8 @@
       <c r="D92" s="3" t="n">
         <v>12189</v>
       </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":21003,"count":1},{"id":12005,"count":1}]}</t>
-        </is>
+      <c r="E92" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":21003,"count":1},{"id":12005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="93">
@@ -2402,10 +2220,8 @@
       <c r="D93" s="3" t="n">
         <v>12189</v>
       </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":13005,"count":1},{"id":15005,"count":1}]}</t>
-        </is>
+      <c r="E93" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":13005,"count":1},{"id":15005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="94">
@@ -2423,10 +2239,8 @@
       <c r="D94" s="3" t="n">
         <v>11081</v>
       </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":17005,"count":1},{"id":18005,"count":1}]}</t>
-        </is>
+      <c r="E94" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":17005,"count":1},{"id":18005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="95">
@@ -2444,10 +2258,8 @@
       <c r="D95" s="3" t="n">
         <v>11081</v>
       </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":14003,"count":1},{"id":11005,"count":1}]}</t>
-        </is>
+      <c r="E95" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":14003,"count":1},{"id":11005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="96">
@@ -2465,10 +2277,8 @@
       <c r="D96" s="3" t="n">
         <v>11081</v>
       </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":21003,"count":1},{"id":12005,"count":1}]}</t>
-        </is>
+      <c r="E96" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":21003,"count":1},{"id":12005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="97">
@@ -2486,10 +2296,8 @@
       <c r="D97" s="3" t="n">
         <v>12189</v>
       </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":13005,"count":1},{"id":15006,"count":1}]}</t>
-        </is>
+      <c r="E97" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":13005,"count":1},{"id":15006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="98">
@@ -2507,10 +2315,8 @@
       <c r="D98" s="3" t="n">
         <v>11081</v>
       </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":28}],"items":[{"id":17006,"count":1},{"id":18006,"count":1}]}</t>
-        </is>
+      <c r="E98" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":28}],"items":[{"id":17006,"count":1},{"id":18006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="99">
@@ -2528,10 +2334,8 @@
       <c r="D99" s="3" t="n">
         <v>11081</v>
       </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":14003,"count":1},{"id":11006,"count":1}]}</t>
-        </is>
+      <c r="E99" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":14003,"count":1},{"id":11006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="100">
@@ -2549,10 +2353,8 @@
       <c r="D100" s="3" t="n">
         <v>11081</v>
       </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":21003,"count":1},{"id":12006,"count":1}]}</t>
-        </is>
+      <c r="E100" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":25},{"token":3,"amount":28}],"items":[{"id":21003,"count":1},{"id":12006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="101">
@@ -2570,10 +2372,8 @@
       <c r="D101" s="3" t="n">
         <v>11081</v>
       </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":13006,"count":1},{"id":15006,"count":1}]}</t>
-        </is>
+      <c r="E101" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":26},{"token":3,"amount":29}],"items":[{"id":13006,"count":1},{"id":15006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="102">
@@ -2591,10 +2391,8 @@
       <c r="D102" s="3" t="n">
         <v>11286</v>
       </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":23001,"count":1},{"id":11006,"count":1}]}</t>
-        </is>
+      <c r="E102" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":23001,"count":1},{"id":11006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="103">
@@ -2612,10 +2410,8 @@
       <c r="D103" s="3" t="n">
         <v>11286</v>
       </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":27}],"items":[{"id":20001,"count":1},{"id":12006,"count":1}]}</t>
-        </is>
+      <c r="E103" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":27}],"items":[{"id":20001,"count":1},{"id":12006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="104">
@@ -2633,10 +2429,8 @@
       <c r="D104" s="3" t="n">
         <v>12312</v>
       </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":13006,"count":1},{"id":14003,"count":1}]}</t>
-        </is>
+      <c r="E104" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":13006,"count":1},{"id":14003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="105">
@@ -2654,10 +2448,8 @@
       <c r="D105" s="3" t="n">
         <v>11286</v>
       </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":15006,"count":1},{"id":17006,"count":1}]}</t>
-        </is>
+      <c r="E105" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":15006,"count":1},{"id":17006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="106">
@@ -2675,10 +2467,8 @@
       <c r="D106" s="3" t="n">
         <v>11286</v>
       </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":18006,"count":1},{"id":21004,"count":1}]}</t>
-        </is>
+      <c r="E106" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":18006,"count":1},{"id":21004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="107">
@@ -2696,10 +2486,8 @@
       <c r="D107" s="3" t="n">
         <v>11286</v>
       </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":23001,"count":1},{"id":11006,"count":1}]}</t>
-        </is>
+      <c r="E107" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":23001,"count":1},{"id":11006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="108">
@@ -2717,10 +2505,8 @@
       <c r="D108" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":20001,"count":1},{"id":12006,"count":1}]}</t>
-        </is>
+      <c r="E108" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":20001,"count":1},{"id":12006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="109">
@@ -2738,10 +2524,8 @@
       <c r="D109" s="3" t="n">
         <v>15049</v>
       </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":13006,"count":1},{"id":14004,"count":1}]}</t>
-        </is>
+      <c r="E109" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":13006,"count":1},{"id":14004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="110">
@@ -2759,10 +2543,8 @@
       <c r="D110" s="3" t="n">
         <v>15049</v>
       </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":15006,"count":1},{"id":17006,"count":1}]}</t>
-        </is>
+      <c r="E110" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":15006,"count":1},{"id":17006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="111">
@@ -2780,10 +2562,8 @@
       <c r="D111" s="3" t="n">
         <v>15049</v>
       </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":18006,"count":1},{"id":21004,"count":1}]}</t>
-        </is>
+      <c r="E111" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":18006,"count":1},{"id":21004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="112">
@@ -2801,10 +2581,8 @@
       <c r="D112" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":23002,"count":1},{"id":11006,"count":1}]}</t>
-        </is>
+      <c r="E112" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":23002,"count":1},{"id":11006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="113">
@@ -2822,10 +2600,8 @@
       <c r="D113" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":20002,"count":1},{"id":12006,"count":1}]}</t>
-        </is>
+      <c r="E113" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":20002,"count":1},{"id":12006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="114">
@@ -2843,10 +2619,8 @@
       <c r="D114" s="3" t="n">
         <v>15049</v>
       </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":13006,"count":1},{"id":14004,"count":1}]}</t>
-        </is>
+      <c r="E114" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":13006,"count":1},{"id":14004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="115">
@@ -2864,10 +2638,8 @@
       <c r="D115" s="3" t="n">
         <v>15049</v>
       </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":15006,"count":1},{"id":17006,"count":1}]}</t>
-        </is>
+      <c r="E115" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":15006,"count":1},{"id":17006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="116">
@@ -2885,10 +2657,8 @@
       <c r="D116" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":18006,"count":1},{"id":21004,"count":1}]}</t>
-        </is>
+      <c r="E116" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":18006,"count":1},{"id":21004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="117">
@@ -2906,10 +2676,8 @@
       <c r="D117" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":23002,"count":1},{"id":11006,"count":1}]}</t>
-        </is>
+      <c r="E117" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":23002,"count":1},{"id":11006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="118">
@@ -2927,10 +2695,8 @@
       <c r="D118" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":20002,"count":1},{"id":12006,"count":1}]}</t>
-        </is>
+      <c r="E118" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":20002,"count":1},{"id":12006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="119">
@@ -2948,10 +2714,8 @@
       <c r="D119" s="3" t="n">
         <v>15049</v>
       </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":27}],"items":[{"id":13006,"count":1},{"id":14004,"count":1}]}</t>
-        </is>
+      <c r="E119" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":27}],"items":[{"id":13006,"count":1},{"id":14004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="120">
@@ -2969,10 +2733,8 @@
       <c r="D120" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":15006,"count":1},{"id":17006,"count":1}]}</t>
-        </is>
+      <c r="E120" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":15006,"count":1},{"id":17006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="121">
@@ -2990,10 +2752,8 @@
       <c r="D121" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":18006,"count":1},{"id":21005,"count":1}]}</t>
-        </is>
+      <c r="E121" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":18006,"count":1},{"id":21005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="122">
@@ -3011,10 +2771,8 @@
       <c r="D122" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":27}],"items":[{"id":23003,"count":1},{"id":11006,"count":1}]}</t>
-        </is>
+      <c r="E122" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":27}],"items":[{"id":23003,"count":1},{"id":11006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="123">
@@ -3032,10 +2790,8 @@
       <c r="D123" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":20003,"count":1},{"id":12006,"count":1}]}</t>
-        </is>
+      <c r="E123" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":20003,"count":1},{"id":12006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="124">
@@ -3053,10 +2809,8 @@
       <c r="D124" s="3" t="n">
         <v>12312</v>
       </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":13006,"count":1},{"id":14005,"count":1}]}</t>
-        </is>
+      <c r="E124" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":13006,"count":1},{"id":14005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="125">
@@ -3074,10 +2828,8 @@
       <c r="D125" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":15006,"count":1},{"id":17006,"count":1}]}</t>
-        </is>
+      <c r="E125" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":15006,"count":1},{"id":17006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="126">
@@ -3095,10 +2847,8 @@
       <c r="D126" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":18006,"count":1},{"id":21005,"count":1}]}</t>
-        </is>
+      <c r="E126" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":18006,"count":1},{"id":21005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="127">
@@ -3116,10 +2866,8 @@
       <c r="D127" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":23003,"count":1},{"id":11006,"count":1}]}</t>
-        </is>
+      <c r="E127" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":23003,"count":1},{"id":11006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="128">
@@ -3137,10 +2885,8 @@
       <c r="D128" s="3" t="n">
         <v>12312</v>
       </c>
-      <c r="E128" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":20003,"count":1},{"id":12006,"count":1}]}</t>
-        </is>
+      <c r="E128" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":20003,"count":1},{"id":12006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="129">
@@ -3158,10 +2904,8 @@
       <c r="D129" s="3" t="n">
         <v>12312</v>
       </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":13006,"count":1},{"id":14005,"count":1}]}</t>
-        </is>
+      <c r="E129" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":13006,"count":1},{"id":14005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="130">
@@ -3179,10 +2923,8 @@
       <c r="D130" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":15007,"count":1},{"id":17006,"count":1}]}</t>
-        </is>
+      <c r="E130" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":15007,"count":1},{"id":17006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="131">
@@ -3200,10 +2942,8 @@
       <c r="D131" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":18006,"count":1},{"id":21005,"count":1}]}</t>
-        </is>
+      <c r="E131" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":18006,"count":1},{"id":21005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="132">
@@ -3221,10 +2961,8 @@
       <c r="D132" s="3" t="n">
         <v>12312</v>
       </c>
-      <c r="E132" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":23004,"count":1},{"id":11006,"count":1}]}</t>
-        </is>
+      <c r="E132" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":23004,"count":1},{"id":11006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="133">
@@ -3242,10 +2980,8 @@
       <c r="D133" s="3" t="n">
         <v>12312</v>
       </c>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":20004,"count":1},{"id":12007,"count":1}]}</t>
-        </is>
+      <c r="E133" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":20004,"count":1},{"id":12007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="134">
@@ -3263,10 +2999,8 @@
       <c r="D134" s="3" t="n">
         <v>12312</v>
       </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":13007,"count":1},{"id":14005,"count":1}]}</t>
-        </is>
+      <c r="E134" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":13007,"count":1},{"id":14005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="135">
@@ -3284,10 +3018,8 @@
       <c r="D135" s="3" t="n">
         <v>13544</v>
       </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":15007,"count":1},{"id":17007,"count":1}]}</t>
-        </is>
+      <c r="E135" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":27}],"items":[{"id":15007,"count":1},{"id":17007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="136">
@@ -3305,10 +3037,8 @@
       <c r="D136" s="3" t="n">
         <v>12312</v>
       </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":18007,"count":1},{"id":21006,"count":1}]}</t>
-        </is>
+      <c r="E136" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":26}],"items":[{"id":18007,"count":1},{"id":21006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="137">
@@ -3326,10 +3056,8 @@
       <c r="D137" s="3" t="n">
         <v>12312</v>
       </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":23004,"count":1},{"id":11007,"count":1}]}</t>
-        </is>
+      <c r="E137" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":23004,"count":1},{"id":11007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="138">
@@ -3347,10 +3075,8 @@
       <c r="D138" s="3" t="n">
         <v>12312</v>
       </c>
-      <c r="E138" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":27}],"items":[{"id":20004,"count":1},{"id":12007,"count":1}]}</t>
-        </is>
+      <c r="E138" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":56},{"token":3,"amount":27}],"items":[{"id":20004,"count":1},{"id":12007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="139">
@@ -3368,10 +3094,8 @@
       <c r="D139" s="3" t="n">
         <v>12312</v>
       </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":13007,"count":1},{"id":14006,"count":1}]}</t>
-        </is>
+      <c r="E139" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":57},{"token":3,"amount":26}],"items":[{"id":13007,"count":1},{"id":14006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="140">
@@ -3389,10 +3113,8 @@
       <c r="D140" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":16001,"count":1},{"id":24001,"count":1}]}</t>
-        </is>
+      <c r="E140" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":16001,"count":1},{"id":24001,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="141">
@@ -3410,10 +3132,8 @@
       <c r="D141" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":11007,"count":1},{"id":19001,"count":1}]}</t>
-        </is>
+      <c r="E141" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":11007,"count":1},{"id":19001,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="142">
@@ -3431,10 +3151,8 @@
       <c r="D142" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E142" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":12007,"count":1},{"id":13007,"count":1}]}</t>
-        </is>
+      <c r="E142" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":12007,"count":1},{"id":13007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="143">
@@ -3452,10 +3170,8 @@
       <c r="D143" s="3" t="n">
         <v>20950</v>
       </c>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":14006,"count":1},{"id":15007,"count":1}]}</t>
-        </is>
+      <c r="E143" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":14006,"count":1},{"id":15007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="144">
@@ -3473,10 +3189,8 @@
       <c r="D144" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E144" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":96},{"token":3,"amount":24}],"items":[{"id":17007,"count":1},{"id":18007,"count":1}]}</t>
-        </is>
+      <c r="E144" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":96},{"token":3,"amount":24}],"items":[{"id":17007,"count":1},{"id":18007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="145">
@@ -3494,10 +3208,8 @@
       <c r="D145" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":20005,"count":1},{"id":21006,"count":1}]}</t>
-        </is>
+      <c r="E145" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":20005,"count":1},{"id":21006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="146">
@@ -3515,10 +3227,8 @@
       <c r="D146" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":23005,"count":1},{"id":16002,"count":1}]}</t>
-        </is>
+      <c r="E146" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":23005,"count":1},{"id":16002,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="147">
@@ -3536,10 +3246,8 @@
       <c r="D147" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E147" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":24002,"count":1},{"id":11007,"count":1}]}</t>
-        </is>
+      <c r="E147" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":24002,"count":1},{"id":11007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="148">
@@ -3557,10 +3265,8 @@
       <c r="D148" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E148" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":19002,"count":1},{"id":12007,"count":1}]}</t>
-        </is>
+      <c r="E148" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":19002,"count":1},{"id":12007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="149">
@@ -3578,10 +3284,8 @@
       <c r="D149" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":13007,"count":1},{"id":14006,"count":1}]}</t>
-        </is>
+      <c r="E149" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":13007,"count":1},{"id":14006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="150">
@@ -3599,10 +3303,8 @@
       <c r="D150" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":15007,"count":1},{"id":17007,"count":1}]}</t>
-        </is>
+      <c r="E150" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":15007,"count":1},{"id":17007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="151">
@@ -3620,10 +3322,8 @@
       <c r="D151" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":18007,"count":1},{"id":20005,"count":1}]}</t>
-        </is>
+      <c r="E151" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":18007,"count":1},{"id":20005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="152">
@@ -3641,10 +3341,8 @@
       <c r="D152" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":96},{"token":3,"amount":24}],"items":[{"id":21006,"count":1},{"id":23005,"count":1}]}</t>
-        </is>
+      <c r="E152" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":96},{"token":3,"amount":24}],"items":[{"id":21006,"count":1},{"id":23005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="153">
@@ -3662,10 +3360,8 @@
       <c r="D153" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":16003,"count":1},{"id":24003,"count":1}]}</t>
-        </is>
+      <c r="E153" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":16003,"count":1},{"id":24003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="154">
@@ -3683,10 +3379,8 @@
       <c r="D154" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":11007,"count":1},{"id":19003,"count":1}]}</t>
-        </is>
+      <c r="E154" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":11007,"count":1},{"id":19003,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="155">
@@ -3704,10 +3398,8 @@
       <c r="D155" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":12007,"count":1},{"id":13007,"count":1}]}</t>
-        </is>
+      <c r="E155" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":12007,"count":1},{"id":13007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="156">
@@ -3725,10 +3417,8 @@
       <c r="D156" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E156" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":14007,"count":1},{"id":15007,"count":1}]}</t>
-        </is>
+      <c r="E156" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":14007,"count":1},{"id":15007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="157">
@@ -3746,10 +3436,8 @@
       <c r="D157" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":17007,"count":1},{"id":18007,"count":1}]}</t>
-        </is>
+      <c r="E157" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":17007,"count":1},{"id":18007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="158">
@@ -3767,10 +3455,8 @@
       <c r="D158" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E158" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":20006,"count":1},{"id":21007,"count":1}]}</t>
-        </is>
+      <c r="E158" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":20006,"count":1},{"id":21007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="159">
@@ -3788,10 +3474,8 @@
       <c r="D159" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E159" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":23006,"count":1},{"id":16004,"count":1}]}</t>
-        </is>
+      <c r="E159" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":23006,"count":1},{"id":16004,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="160">
@@ -3809,10 +3493,8 @@
       <c r="D160" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E160" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":96},{"token":3,"amount":24}],"items":[{"id":24004,"count":1},{"id":11007,"count":1}]}</t>
-        </is>
+      <c r="E160" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":96},{"token":3,"amount":24}],"items":[{"id":24004,"count":1},{"id":11007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="161">
@@ -3830,10 +3512,8 @@
       <c r="D161" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E161" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":19004,"count":1},{"id":12007,"count":1}]}</t>
-        </is>
+      <c r="E161" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":19004,"count":1},{"id":12007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="162">
@@ -3851,10 +3531,8 @@
       <c r="D162" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E162" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":13007,"count":1},{"id":14007,"count":1}]}</t>
-        </is>
+      <c r="E162" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":13007,"count":1},{"id":14007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="163">
@@ -3872,10 +3550,8 @@
       <c r="D163" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E163" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":15007,"count":1},{"id":17007,"count":1}]}</t>
-        </is>
+      <c r="E163" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":15007,"count":1},{"id":17007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="164">
@@ -3893,10 +3569,8 @@
       <c r="D164" s="3" t="n">
         <v>15237</v>
       </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":18007,"count":1},{"id":20006,"count":1}]}</t>
-        </is>
+      <c r="E164" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":18007,"count":1},{"id":20006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="165">
@@ -3914,10 +3588,8 @@
       <c r="D165" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":21007,"count":1},{"id":23006,"count":1}]}</t>
-        </is>
+      <c r="E165" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":21007,"count":1},{"id":23006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="166">
@@ -3935,10 +3607,8 @@
       <c r="D166" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":16005,"count":1},{"id":24005,"count":1}]}</t>
-        </is>
+      <c r="E166" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":16005,"count":1},{"id":24005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="167">
@@ -3956,10 +3626,8 @@
       <c r="D167" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E167" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":11007,"count":1},{"id":19005,"count":1}]}</t>
-        </is>
+      <c r="E167" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":11007,"count":1},{"id":19005,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="168">
@@ -3977,10 +3645,8 @@
       <c r="D168" s="3" t="n">
         <v>15237</v>
       </c>
-      <c r="E168" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":96},{"token":3,"amount":24}],"items":[{"id":12007,"count":1},{"id":13007,"count":1}]}</t>
-        </is>
+      <c r="E168" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":96},{"token":3,"amount":24}],"items":[{"id":12007,"count":1},{"id":13007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="169">
@@ -3998,10 +3664,8 @@
       <c r="D169" s="3" t="n">
         <v>15237</v>
       </c>
-      <c r="E169" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":14007,"count":1},{"id":15007,"count":1}]}</t>
-        </is>
+      <c r="E169" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":14007,"count":1},{"id":15007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="170">
@@ -4019,10 +3683,8 @@
       <c r="D170" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E170" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":17007,"count":1},{"id":18007,"count":1}]}</t>
-        </is>
+      <c r="E170" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":17007,"count":1},{"id":18007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="171">
@@ -4040,10 +3702,8 @@
       <c r="D171" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":20007,"count":1},{"id":21007,"count":1}]}</t>
-        </is>
+      <c r="E171" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":20007,"count":1},{"id":21007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="172">
@@ -4061,10 +3721,8 @@
       <c r="D172" s="3" t="n">
         <v>15237</v>
       </c>
-      <c r="E172" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":23007,"count":1},{"id":16006,"count":1}]}</t>
-        </is>
+      <c r="E172" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":23007,"count":1},{"id":16006,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="173">
@@ -4082,10 +3740,8 @@
       <c r="D173" s="3" t="n">
         <v>15237</v>
       </c>
-      <c r="E173" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":24006,"count":1},{"id":11007,"count":1}]}</t>
-        </is>
+      <c r="E173" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":24006,"count":1},{"id":11007,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="174">
@@ -4103,10 +3759,8 @@
       <c r="D174" s="3" t="n">
         <v>15237</v>
       </c>
-      <c r="E174" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":19006,"count":1},{"id":12008,"count":1}]}</t>
-        </is>
+      <c r="E174" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":19006,"count":1},{"id":12008,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="175">
@@ -4124,10 +3778,8 @@
       <c r="D175" s="3" t="n">
         <v>16760</v>
       </c>
-      <c r="E175" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":13008,"count":1},{"id":14008,"count":1}]}</t>
-        </is>
+      <c r="E175" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":13008,"count":1},{"id":14008,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="176">
@@ -4145,10 +3797,8 @@
       <c r="D176" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E176" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":96},{"token":3,"amount":24}],"items":[{"id":15008,"count":1},{"id":17008,"count":1}]}</t>
-        </is>
+      <c r="E176" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":96},{"token":3,"amount":24}],"items":[{"id":15008,"count":1},{"id":17008,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="177">
@@ -4166,10 +3816,8 @@
       <c r="D177" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":18008,"count":1},{"id":20008,"count":1}]}</t>
-        </is>
+      <c r="E177" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":18008,"count":1},{"id":20008,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="178">
@@ -4187,10 +3835,8 @@
       <c r="D178" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":21008,"count":1},{"id":23008,"count":1}]}</t>
-        </is>
+      <c r="E178" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":21008,"count":1},{"id":23008,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="179">
@@ -4208,10 +3854,8 @@
       <c r="D179" s="3" t="n">
         <v>18623</v>
       </c>
-      <c r="E179" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":16008,"count":1},{"id":24008,"count":1}]}</t>
-        </is>
+      <c r="E179" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":25}],"items":[{"id":16008,"count":1},{"id":24008,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="180">
@@ -4229,10 +3873,8 @@
       <c r="D180" s="3" t="n">
         <v>20950</v>
       </c>
-      <c r="E180" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":11008,"count":1},{"id":19008,"count":1}]}</t>
-        </is>
+      <c r="E180" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":95},{"token":3,"amount":24}],"items":[{"id":11008,"count":1},{"id":19008,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="181">
@@ -4250,10 +3892,8 @@
       <c r="D181" s="3" t="n">
         <v>368660</v>
       </c>
-      <c r="E181" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":11009,"count":1},{"id":12009,"count":1}]}</t>
-        </is>
+      <c r="E181" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":11009,"count":1},{"id":12009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="182">
@@ -4271,10 +3911,8 @@
       <c r="D182" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E182" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":13009,"count":1},{"id":14009,"count":1}]}</t>
-        </is>
+      <c r="E182" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":13009,"count":1},{"id":14009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="183">
@@ -4292,10 +3930,8 @@
       <c r="D183" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":15009,"count":1},{"id":16009,"count":1}]}</t>
-        </is>
+      <c r="E183" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":15009,"count":1},{"id":16009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="184">
@@ -4313,10 +3949,8 @@
       <c r="D184" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E184" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":23009,"count":1},{"id":24009,"count":1}]}</t>
-        </is>
+      <c r="E184" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":23009,"count":1},{"id":24009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="185">
@@ -4334,10 +3968,8 @@
       <c r="D185" s="3" t="n">
         <v>368660</v>
       </c>
-      <c r="E185" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":17009,"count":1},{"id":18009,"count":1}]}</t>
-        </is>
+      <c r="E185" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":17009,"count":1},{"id":18009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="186">
@@ -4355,10 +3987,8 @@
       <c r="D186" s="3" t="n">
         <v>368660</v>
       </c>
-      <c r="E186" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":19009,"count":1},{"id":20009,"count":1}]}</t>
-        </is>
+      <c r="E186" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":19009,"count":1},{"id":20009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="187">
@@ -4376,10 +4006,8 @@
       <c r="D187" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E187" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":21009,"count":1},{"id":11009,"count":1}]}</t>
-        </is>
+      <c r="E187" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":21009,"count":1},{"id":11009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="188">
@@ -4397,10 +4025,8 @@
       <c r="D188" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E188" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":12009,"count":1},{"id":13009,"count":1}]}</t>
-        </is>
+      <c r="E188" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":12009,"count":1},{"id":13009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="189">
@@ -4418,10 +4044,8 @@
       <c r="D189" s="3" t="n">
         <v>368660</v>
       </c>
-      <c r="E189" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":14009,"count":1},{"id":15009,"count":1}]}</t>
-        </is>
+      <c r="E189" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":14009,"count":1},{"id":15009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="190">
@@ -4439,10 +4063,8 @@
       <c r="D190" s="3" t="n">
         <v>368660</v>
       </c>
-      <c r="E190" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":16009,"count":1},{"id":23009,"count":1}]}</t>
-        </is>
+      <c r="E190" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":16009,"count":1},{"id":23009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="191">
@@ -4460,10 +4082,8 @@
       <c r="D191" s="3" t="n">
         <v>368660</v>
       </c>
-      <c r="E191" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":24009,"count":1},{"id":17009,"count":1}]}</t>
-        </is>
+      <c r="E191" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":24009,"count":1},{"id":17009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="192">
@@ -4481,10 +4101,8 @@
       <c r="D192" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":18009,"count":1},{"id":19009,"count":1}]}</t>
-        </is>
+      <c r="E192" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":18009,"count":1},{"id":19009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="193">
@@ -4502,10 +4120,8 @@
       <c r="D193" s="3" t="n">
         <v>368660</v>
       </c>
-      <c r="E193" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":20009,"count":1},{"id":21009,"count":1}]}</t>
-        </is>
+      <c r="E193" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":20009,"count":1},{"id":21009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="194">
@@ -4523,10 +4139,8 @@
       <c r="D194" s="3" t="n">
         <v>368660</v>
       </c>
-      <c r="E194" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":11009,"count":1},{"id":12009,"count":1}]}</t>
-        </is>
+      <c r="E194" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":11009,"count":1},{"id":12009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="195">
@@ -4544,10 +4158,8 @@
       <c r="D195" s="3" t="n">
         <v>368660</v>
       </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":13009,"count":1},{"id":14009,"count":1}]}</t>
-        </is>
+      <c r="E195" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":13009,"count":1},{"id":14009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="196">
@@ -4565,10 +4177,8 @@
       <c r="D196" s="3" t="n">
         <v>368660</v>
       </c>
-      <c r="E196" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":15009,"count":1},{"id":16009,"count":1}]}</t>
-        </is>
+      <c r="E196" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":15009,"count":1},{"id":16009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="197">
@@ -4586,10 +4196,8 @@
       <c r="D197" s="3" t="n">
         <v>340302</v>
       </c>
-      <c r="E197" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":23009,"count":1},{"id":24009,"count":1}]}</t>
-        </is>
+      <c r="E197" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":23009,"count":1},{"id":24009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="198">
@@ -4607,10 +4215,8 @@
       <c r="D198" s="3" t="n">
         <v>368660</v>
       </c>
-      <c r="E198" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":17009,"count":1},{"id":18009,"count":1}]}</t>
-        </is>
+      <c r="E198" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":17009,"count":1},{"id":18009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="199">
@@ -4628,10 +4234,8 @@
       <c r="D199" s="3" t="n">
         <v>368660</v>
       </c>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":19009,"count":1},{"id":20009,"count":1}]}</t>
-        </is>
+      <c r="E199" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":19009,"count":1},{"id":20009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="200">
@@ -4649,10 +4253,8 @@
       <c r="D200" s="3" t="n">
         <v>368660</v>
       </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":21009,"count":1},{"id":11009,"count":1}]}</t>
-        </is>
+      <c r="E200" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":21009,"count":1},{"id":11009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="201">
@@ -4670,10 +4272,8 @@
       <c r="D201" s="3" t="n">
         <v>340302</v>
       </c>
-      <c r="E201" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":12009,"count":1},{"id":13009,"count":1}]}</t>
-        </is>
+      <c r="E201" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":12009,"count":1},{"id":13009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="202">
@@ -4691,10 +4291,8 @@
       <c r="D202" s="3" t="n">
         <v>340302</v>
       </c>
-      <c r="E202" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":14009,"count":1},{"id":15009,"count":1}]}</t>
-        </is>
+      <c r="E202" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":14009,"count":1},{"id":15009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="203">
@@ -4712,10 +4310,8 @@
       <c r="D203" s="3" t="n">
         <v>368660</v>
       </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":16009,"count":1},{"id":23009,"count":1}]}</t>
-        </is>
+      <c r="E203" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":16009,"count":1},{"id":23009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="204">
@@ -4733,10 +4329,8 @@
       <c r="D204" s="3" t="n">
         <v>368660</v>
       </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":24009,"count":1},{"id":17009,"count":1}]}</t>
-        </is>
+      <c r="E204" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":24009,"count":1},{"id":17009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="205">
@@ -4754,10 +4348,8 @@
       <c r="D205" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":18009,"count":1},{"id":19009,"count":1}]}</t>
-        </is>
+      <c r="E205" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":18009,"count":1},{"id":19009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="206">
@@ -4775,10 +4367,8 @@
       <c r="D206" s="3" t="n">
         <v>442392</v>
       </c>
-      <c r="E206" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":20009,"count":1},{"id":21009,"count":1}]}</t>
-        </is>
+      <c r="E206" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":20009,"count":1},{"id":21009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="207">
@@ -4796,10 +4386,8 @@
       <c r="D207" s="3" t="n">
         <v>442392</v>
       </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":11009,"count":1},{"id":12009,"count":1}]}</t>
-        </is>
+      <c r="E207" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":11009,"count":1},{"id":12009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="208">
@@ -4817,10 +4405,8 @@
       <c r="D208" s="3" t="n">
         <v>442392</v>
       </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":13009,"count":1},{"id":14009,"count":1}]}</t>
-        </is>
+      <c r="E208" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":13009,"count":1},{"id":14009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="209">
@@ -4838,10 +4424,8 @@
       <c r="D209" s="3" t="n">
         <v>442392</v>
       </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":15009,"count":1},{"id":16009,"count":1}]}</t>
-        </is>
+      <c r="E209" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":15009,"count":1},{"id":16009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="210">
@@ -4859,10 +4443,8 @@
       <c r="D210" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E210" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":23009,"count":1},{"id":24009,"count":1}]}</t>
-        </is>
+      <c r="E210" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":23009,"count":1},{"id":24009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="211">
@@ -4880,10 +4462,8 @@
       <c r="D211" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E211" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":17009,"count":1},{"id":18009,"count":1}]}</t>
-        </is>
+      <c r="E211" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":17009,"count":1},{"id":18009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="212">
@@ -4901,10 +4481,8 @@
       <c r="D212" s="3" t="n">
         <v>442392</v>
       </c>
-      <c r="E212" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":19009,"count":1},{"id":20009,"count":1}]}</t>
-        </is>
+      <c r="E212" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":19009,"count":1},{"id":20009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="213">
@@ -4922,10 +4500,8 @@
       <c r="D213" s="3" t="n">
         <v>442392</v>
       </c>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":21009,"count":1},{"id":11009,"count":1}]}</t>
-        </is>
+      <c r="E213" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":21009,"count":1},{"id":11009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="214">
@@ -4943,10 +4519,8 @@
       <c r="D214" s="3" t="n">
         <v>442392</v>
       </c>
-      <c r="E214" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":12009,"count":1},{"id":13009,"count":1}]}</t>
-        </is>
+      <c r="E214" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":12009,"count":1},{"id":13009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="215">
@@ -4964,10 +4538,8 @@
       <c r="D215" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E215" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":14009,"count":1},{"id":15009,"count":1}]}</t>
-        </is>
+      <c r="E215" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":14009,"count":1},{"id":15009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="216">
@@ -4985,10 +4557,8 @@
       <c r="D216" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E216" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":16009,"count":1},{"id":23009,"count":1}]}</t>
-        </is>
+      <c r="E216" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":16009,"count":1},{"id":23009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="217">
@@ -5006,10 +4576,8 @@
       <c r="D217" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":24009,"count":1},{"id":17009,"count":1}]}</t>
-        </is>
+      <c r="E217" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":24009,"count":1},{"id":17009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="218">
@@ -5027,10 +4595,8 @@
       <c r="D218" s="3" t="n">
         <v>442392</v>
       </c>
-      <c r="E218" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":18009,"count":1},{"id":19009,"count":1}]}</t>
-        </is>
+      <c r="E218" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":18009,"count":1},{"id":19009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="219">
@@ -5048,10 +4614,8 @@
       <c r="D219" s="3" t="n">
         <v>442392</v>
       </c>
-      <c r="E219" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":20009,"count":1},{"id":21009,"count":1}]}</t>
-        </is>
+      <c r="E219" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":20009,"count":1},{"id":21009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="220">
@@ -5069,10 +4633,8 @@
       <c r="D220" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E220" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":11009,"count":1},{"id":12009,"count":1}]}</t>
-        </is>
+      <c r="E220" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":11009,"count":1},{"id":12009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="221">
@@ -5090,10 +4652,8 @@
       <c r="D221" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E221" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":13009,"count":1},{"id":14009,"count":1}]}</t>
-        </is>
+      <c r="E221" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":13009,"count":1},{"id":14009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="222">
@@ -5111,10 +4671,8 @@
       <c r="D222" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E222" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":15009,"count":1},{"id":16009,"count":1}]}</t>
-        </is>
+      <c r="E222" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":15009,"count":1},{"id":16009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="223">
@@ -5132,10 +4690,8 @@
       <c r="D223" s="3" t="n">
         <v>402175</v>
       </c>
-      <c r="E223" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":23009,"count":1},{"id":24009,"count":1}]}</t>
-        </is>
+      <c r="E223" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":22}],"items":[{"id":23009,"count":1},{"id":24009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="224">
@@ -5153,10 +4709,8 @@
       <c r="D224" s="3" t="n">
         <v>442392</v>
       </c>
-      <c r="E224" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":17009,"count":1},{"id":18009,"count":1}]}</t>
-        </is>
+      <c r="E224" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":50},{"token":3,"amount":23}],"items":[{"id":17009,"count":1},{"id":18009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="225">
@@ -5174,10 +4728,8 @@
       <c r="D225" s="3" t="n">
         <v>399382</v>
       </c>
-      <c r="E225" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":11009,"count":1},{"id":12009,"count":1}]}</t>
-        </is>
+      <c r="E225" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":11009,"count":1},{"id":12009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="226">
@@ -5195,10 +4747,8 @@
       <c r="D226" s="3" t="n">
         <v>435689</v>
       </c>
-      <c r="E226" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":13009,"count":1},{"id":14009,"count":1}]}</t>
-        </is>
+      <c r="E226" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":13009,"count":1},{"id":14009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="227">
@@ -5216,10 +4766,8 @@
       <c r="D227" s="3" t="n">
         <v>435689</v>
       </c>
-      <c r="E227" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":20}],"items":[{"id":15009,"count":1},{"id":16010,"count":1}]}</t>
-        </is>
+      <c r="E227" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":20}],"items":[{"id":15009,"count":1},{"id":16010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="228">
@@ -5237,10 +4785,8 @@
       <c r="D228" s="3" t="n">
         <v>435689</v>
       </c>
-      <c r="E228" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":23010,"count":1},{"id":24010,"count":1}]}</t>
-        </is>
+      <c r="E228" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":23010,"count":1},{"id":24010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="229">
@@ -5258,10 +4804,8 @@
       <c r="D229" s="3" t="n">
         <v>399382</v>
       </c>
-      <c r="E229" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":17010,"count":1},{"id":18010,"count":1}]}</t>
-        </is>
+      <c r="E229" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":17010,"count":1},{"id":18010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="230">
@@ -5279,10 +4823,8 @@
       <c r="D230" s="3" t="n">
         <v>399382</v>
       </c>
-      <c r="E230" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":19009,"count":1},{"id":20009,"count":1}]}</t>
-        </is>
+      <c r="E230" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":19009,"count":1},{"id":20009,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="231">
@@ -5300,10 +4842,8 @@
       <c r="D231" s="3" t="n">
         <v>435689</v>
       </c>
-      <c r="E231" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":21009,"count":1},{"id":11010,"count":1}]}</t>
-        </is>
+      <c r="E231" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":21009,"count":1},{"id":11010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="232">
@@ -5321,10 +4861,8 @@
       <c r="D232" s="3" t="n">
         <v>435689</v>
       </c>
-      <c r="E232" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":12010,"count":1},{"id":13010,"count":1}]}</t>
-        </is>
+      <c r="E232" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":12010,"count":1},{"id":13010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="233">
@@ -5342,10 +4880,8 @@
       <c r="D233" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E233" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":20}],"items":[{"id":14010,"count":1},{"id":15010,"count":1}]}</t>
-        </is>
+      <c r="E233" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":20}],"items":[{"id":14010,"count":1},{"id":15010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="234">
@@ -5363,10 +4899,8 @@
       <c r="D234" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E234" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":16010,"count":1},{"id":23010,"count":1}]}</t>
-        </is>
+      <c r="E234" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":16010,"count":1},{"id":23010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="235">
@@ -5384,10 +4918,8 @@
       <c r="D235" s="3" t="n">
         <v>532509</v>
       </c>
-      <c r="E235" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":24010,"count":1},{"id":17010,"count":1}]}</t>
-        </is>
+      <c r="E235" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":24010,"count":1},{"id":17010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="236">
@@ -5405,10 +4937,8 @@
       <c r="D236" s="3" t="n">
         <v>532509</v>
       </c>
-      <c r="E236" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":18010,"count":1},{"id":19010,"count":1}]}</t>
-        </is>
+      <c r="E236" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":18010,"count":1},{"id":19010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="237">
@@ -5426,10 +4956,8 @@
       <c r="D237" s="3" t="n">
         <v>532509</v>
       </c>
-      <c r="E237" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":20010,"count":1},{"id":21010,"count":1}]}</t>
-        </is>
+      <c r="E237" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":20010,"count":1},{"id":21010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="238">
@@ -5447,10 +4975,8 @@
       <c r="D238" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E238" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":11010,"count":1},{"id":12010,"count":1}]}</t>
-        </is>
+      <c r="E238" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":11010,"count":1},{"id":12010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="239">
@@ -5468,10 +4994,8 @@
       <c r="D239" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E239" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":20}],"items":[{"id":13010,"count":1},{"id":14010,"count":1}]}</t>
-        </is>
+      <c r="E239" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":20}],"items":[{"id":13010,"count":1},{"id":14010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="240">
@@ -5489,10 +5013,8 @@
       <c r="D240" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E240" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":15010,"count":1},{"id":16010,"count":1}]}</t>
-        </is>
+      <c r="E240" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":15010,"count":1},{"id":16010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="241">
@@ -5510,10 +5032,8 @@
       <c r="D241" s="3" t="n">
         <v>532509</v>
       </c>
-      <c r="E241" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":23010,"count":1},{"id":24010,"count":1}]}</t>
-        </is>
+      <c r="E241" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":23010,"count":1},{"id":24010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="242">
@@ -5531,10 +5051,8 @@
       <c r="D242" s="3" t="n">
         <v>532509</v>
       </c>
-      <c r="E242" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":17010,"count":1},{"id":18010,"count":1}]}</t>
-        </is>
+      <c r="E242" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":17010,"count":1},{"id":18010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="243">
@@ -5552,10 +5070,8 @@
       <c r="D243" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E243" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":19010,"count":1},{"id":20010,"count":1}]}</t>
-        </is>
+      <c r="E243" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":19010,"count":1},{"id":20010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="244">
@@ -5573,10 +5089,8 @@
       <c r="D244" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E244" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":21010,"count":1},{"id":11010,"count":1}]}</t>
-        </is>
+      <c r="E244" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":21010,"count":1},{"id":11010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="245">
@@ -5594,10 +5108,8 @@
       <c r="D245" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E245" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":20}],"items":[{"id":12010,"count":1},{"id":13010,"count":1}]}</t>
-        </is>
+      <c r="E245" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":20}],"items":[{"id":12010,"count":1},{"id":13010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="246">
@@ -5615,10 +5127,8 @@
       <c r="D246" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E246" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":14010,"count":1},{"id":15010,"count":1}]}</t>
-        </is>
+      <c r="E246" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":14010,"count":1},{"id":15010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="247">
@@ -5636,10 +5146,8 @@
       <c r="D247" s="3" t="n">
         <v>532509</v>
       </c>
-      <c r="E247" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":16010,"count":1},{"id":23010,"count":1}]}</t>
-        </is>
+      <c r="E247" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":16010,"count":1},{"id":23010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="248">
@@ -5657,10 +5165,8 @@
       <c r="D248" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E248" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":24010,"count":1},{"id":17010,"count":1}]}</t>
-        </is>
+      <c r="E248" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":24010,"count":1},{"id":17010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="249">
@@ -5678,10 +5184,8 @@
       <c r="D249" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E249" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":18010,"count":1},{"id":19010,"count":1}]}</t>
-        </is>
+      <c r="E249" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":18010,"count":1},{"id":19010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="250">
@@ -5699,10 +5203,8 @@
       <c r="D250" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E250" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":20010,"count":1},{"id":21010,"count":1}]}</t>
-        </is>
+      <c r="E250" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":20010,"count":1},{"id":21010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="251">
@@ -5720,10 +5222,8 @@
       <c r="D251" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E251" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":20}],"items":[{"id":11010,"count":1},{"id":12010,"count":1}]}</t>
-        </is>
+      <c r="E251" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":20}],"items":[{"id":11010,"count":1},{"id":12010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="252">
@@ -5741,10 +5241,8 @@
       <c r="D252" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E252" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":13010,"count":1},{"id":14010,"count":1}]}</t>
-        </is>
+      <c r="E252" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":13010,"count":1},{"id":14010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="253">
@@ -5762,10 +5260,8 @@
       <c r="D253" s="3" t="n">
         <v>435689</v>
       </c>
-      <c r="E253" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":15010,"count":1},{"id":16010,"count":1}]}</t>
-        </is>
+      <c r="E253" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":15010,"count":1},{"id":16010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="254">
@@ -5783,10 +5279,8 @@
       <c r="D254" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E254" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":23010,"count":1},{"id":24010,"count":1}]}</t>
-        </is>
+      <c r="E254" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":23010,"count":1},{"id":24010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="255">
@@ -5804,10 +5298,8 @@
       <c r="D255" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E255" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":17010,"count":1},{"id":18010,"count":1}]}</t>
-        </is>
+      <c r="E255" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":17010,"count":1},{"id":18010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="256">
@@ -5825,10 +5317,8 @@
       <c r="D256" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E256" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":19010,"count":1},{"id":20010,"count":1}]}</t>
-        </is>
+      <c r="E256" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":19010,"count":1},{"id":20010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="257">
@@ -5846,10 +5336,8 @@
       <c r="D257" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E257" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":20}],"items":[{"id":21010,"count":1},{"id":11010,"count":1}]}</t>
-        </is>
+      <c r="E257" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":20}],"items":[{"id":21010,"count":1},{"id":11010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="258">
@@ -5867,10 +5355,8 @@
       <c r="D258" s="3" t="n">
         <v>435689</v>
       </c>
-      <c r="E258" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":12010,"count":1},{"id":13010,"count":1}]}</t>
-        </is>
+      <c r="E258" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":12010,"count":1},{"id":13010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="259">
@@ -5888,10 +5374,8 @@
       <c r="D259" s="3" t="n">
         <v>435689</v>
       </c>
-      <c r="E259" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":14010,"count":1},{"id":15010,"count":1}]}</t>
-        </is>
+      <c r="E259" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":14010,"count":1},{"id":15010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="260">
@@ -5909,10 +5393,8 @@
       <c r="D260" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E260" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":16010,"count":1},{"id":23010,"count":1}]}</t>
-        </is>
+      <c r="E260" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":16010,"count":1},{"id":23010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="261">
@@ -5930,10 +5412,8 @@
       <c r="D261" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E261" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":24010,"count":1},{"id":17010,"count":1}]}</t>
-        </is>
+      <c r="E261" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":24010,"count":1},{"id":17010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="262">
@@ -5951,10 +5431,8 @@
       <c r="D262" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E262" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":18010,"count":1},{"id":19010,"count":1}]}</t>
-        </is>
+      <c r="E262" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":18010,"count":1},{"id":19010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="263">
@@ -5972,10 +5450,8 @@
       <c r="D263" s="3" t="n">
         <v>435689</v>
       </c>
-      <c r="E263" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":20}],"items":[{"id":20010,"count":1},{"id":21010,"count":1}]}</t>
-        </is>
+      <c r="E263" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":20}],"items":[{"id":20010,"count":1},{"id":21010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="264">
@@ -5993,10 +5469,8 @@
       <c r="D264" s="3" t="n">
         <v>435689</v>
       </c>
-      <c r="E264" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":11010,"count":1},{"id":12010,"count":1}]}</t>
-        </is>
+      <c r="E264" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":11010,"count":1},{"id":12010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="265">
@@ -6014,10 +5488,8 @@
       <c r="D265" s="3" t="n">
         <v>435689</v>
       </c>
-      <c r="E265" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":13010,"count":1},{"id":14010,"count":1}]}</t>
-        </is>
+      <c r="E265" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":13010,"count":1},{"id":14010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="266">
@@ -6035,10 +5507,8 @@
       <c r="D266" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E266" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":15010,"count":1},{"id":16010,"count":1}]}</t>
-        </is>
+      <c r="E266" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":15010,"count":1},{"id":16010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="267">
@@ -6056,10 +5526,8 @@
       <c r="D267" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E267" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":23010,"count":1},{"id":24010,"count":1}]}</t>
-        </is>
+      <c r="E267" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":23010,"count":1},{"id":24010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="268">
@@ -6077,10 +5545,8 @@
       <c r="D268" s="3" t="n">
         <v>435689</v>
       </c>
-      <c r="E268" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":17010,"count":1},{"id":18010,"count":1}]}</t>
-        </is>
+      <c r="E268" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":17010,"count":1},{"id":18010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="269">
@@ -6098,10 +5564,8 @@
       <c r="D269" s="3" t="n">
         <v>435689</v>
       </c>
-      <c r="E269" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":20}],"items":[{"id":19010,"count":1},{"id":20010,"count":1}]}</t>
-        </is>
+      <c r="E269" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":20}],"items":[{"id":19010,"count":1},{"id":20010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="270">
@@ -6119,10 +5583,8 @@
       <c r="D270" s="3" t="n">
         <v>435689</v>
       </c>
-      <c r="E270" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":21010,"count":1},{"id":11010,"count":1}]}</t>
-        </is>
+      <c r="E270" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":21010,"count":1},{"id":11010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="271">
@@ -6140,10 +5602,8 @@
       <c r="D271" s="3" t="n">
         <v>435689</v>
       </c>
-      <c r="E271" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":12010,"count":1},{"id":13010,"count":1}]}</t>
-        </is>
+      <c r="E271" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":132},{"token":3,"amount":21}],"items":[{"id":12010,"count":1},{"id":13010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="272">
@@ -6161,10 +5621,8 @@
       <c r="D272" s="3" t="n">
         <v>479258</v>
       </c>
-      <c r="E272" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":14010,"count":1},{"id":15010,"count":1}]}</t>
-        </is>
+      <c r="E272" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":131},{"token":3,"amount":21}],"items":[{"id":14010,"count":1},{"id":15010,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="273">
@@ -6182,10 +5640,8 @@
       <c r="D273" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E273" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":11011,"count":1},{"id":12011,"count":1}]}</t>
-        </is>
+      <c r="E273" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":11011,"count":1},{"id":12011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="274">
@@ -6203,10 +5659,8 @@
       <c r="D274" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E274" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":19}],"items":[{"id":13011,"count":1},{"id":14011,"count":1}]}</t>
-        </is>
+      <c r="E274" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":19}],"items":[{"id":13011,"count":1},{"id":14011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="275">
@@ -6224,10 +5678,8 @@
       <c r="D275" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E275" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":15011,"count":1},{"id":16011,"count":1}]}</t>
-        </is>
+      <c r="E275" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":15011,"count":1},{"id":16011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="276">
@@ -6245,10 +5697,8 @@
       <c r="D276" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E276" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":23011,"count":1},{"id":24011,"count":1}]}</t>
-        </is>
+      <c r="E276" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":23011,"count":1},{"id":24011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="277">
@@ -6266,10 +5716,8 @@
       <c r="D277" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E277" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":17011,"count":1},{"id":18011,"count":1}]}</t>
-        </is>
+      <c r="E277" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":17011,"count":1},{"id":18011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="278">
@@ -6287,10 +5735,8 @@
       <c r="D278" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E278" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":19010,"count":1},{"id":20011,"count":1}]}</t>
-        </is>
+      <c r="E278" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":19010,"count":1},{"id":20011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="279">
@@ -6308,10 +5754,8 @@
       <c r="D279" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E279" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":21011,"count":1},{"id":11011,"count":1}]}</t>
-        </is>
+      <c r="E279" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":21011,"count":1},{"id":11011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="280">
@@ -6329,10 +5773,8 @@
       <c r="D280" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E280" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":12011,"count":1},{"id":13011,"count":1}]}</t>
-        </is>
+      <c r="E280" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":12011,"count":1},{"id":13011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="281">
@@ -6350,10 +5792,8 @@
       <c r="D281" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E281" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":14011,"count":1},{"id":15011,"count":1}]}</t>
-        </is>
+      <c r="E281" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":14011,"count":1},{"id":15011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="282">
@@ -6371,10 +5811,8 @@
       <c r="D282" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E282" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":16011,"count":1},{"id":23011,"count":1}]}</t>
-        </is>
+      <c r="E282" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":16011,"count":1},{"id":23011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="283">
@@ -6392,10 +5830,8 @@
       <c r="D283" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E283" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":24011,"count":1},{"id":17011,"count":1}]}</t>
-        </is>
+      <c r="E283" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":24011,"count":1},{"id":17011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="284">
@@ -6413,10 +5849,8 @@
       <c r="D284" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E284" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":18011,"count":1},{"id":19011,"count":1}]}</t>
-        </is>
+      <c r="E284" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":18011,"count":1},{"id":19011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="285">
@@ -6434,10 +5868,8 @@
       <c r="D285" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E285" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":20011,"count":1},{"id":21011,"count":1}]}</t>
-        </is>
+      <c r="E285" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":20011,"count":1},{"id":21011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="286">
@@ -6455,10 +5887,8 @@
       <c r="D286" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E286" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":11011,"count":1},{"id":12011,"count":1}]}</t>
-        </is>
+      <c r="E286" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":11011,"count":1},{"id":12011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="287">
@@ -6476,10 +5906,8 @@
       <c r="D287" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E287" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":13011,"count":1},{"id":14011,"count":1}]}</t>
-        </is>
+      <c r="E287" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":13011,"count":1},{"id":14011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="288">
@@ -6497,10 +5925,8 @@
       <c r="D288" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E288" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":15011,"count":1},{"id":16011,"count":1}]}</t>
-        </is>
+      <c r="E288" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":15011,"count":1},{"id":16011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="289">
@@ -6518,10 +5944,8 @@
       <c r="D289" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E289" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":19}],"items":[{"id":23011,"count":1},{"id":24011,"count":1}]}</t>
-        </is>
+      <c r="E289" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":19}],"items":[{"id":23011,"count":1},{"id":24011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="290">
@@ -6539,10 +5963,8 @@
       <c r="D290" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E290" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":17011,"count":1},{"id":18011,"count":1}]}</t>
-        </is>
+      <c r="E290" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":17011,"count":1},{"id":18011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="291">
@@ -6560,10 +5982,8 @@
       <c r="D291" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E291" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":19011,"count":1},{"id":20011,"count":1}]}</t>
-        </is>
+      <c r="E291" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":19011,"count":1},{"id":20011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="292">
@@ -6581,10 +6001,8 @@
       <c r="D292" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E292" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":19}],"items":[{"id":21011,"count":1},{"id":11011,"count":1}]}</t>
-        </is>
+      <c r="E292" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":19}],"items":[{"id":21011,"count":1},{"id":11011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="293">
@@ -6602,10 +6020,8 @@
       <c r="D293" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E293" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":12011,"count":1},{"id":13011,"count":1}]}</t>
-        </is>
+      <c r="E293" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":12011,"count":1},{"id":13011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="294">
@@ -6623,10 +6039,8 @@
       <c r="D294" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E294" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":14011,"count":1},{"id":15011,"count":1}]}</t>
-        </is>
+      <c r="E294" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":14011,"count":1},{"id":15011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="295">
@@ -6644,10 +6058,8 @@
       <c r="D295" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E295" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":16011,"count":1},{"id":23011,"count":1}]}</t>
-        </is>
+      <c r="E295" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":16011,"count":1},{"id":23011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="296">
@@ -6665,10 +6077,8 @@
       <c r="D296" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E296" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":24011,"count":1},{"id":17011,"count":1}]}</t>
-        </is>
+      <c r="E296" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":24011,"count":1},{"id":17011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="297">
@@ -6686,10 +6096,8 @@
       <c r="D297" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E297" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":18011,"count":1},{"id":19011,"count":1}]}</t>
-        </is>
+      <c r="E297" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":18011,"count":1},{"id":19011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="298">
@@ -6707,10 +6115,8 @@
       <c r="D298" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E298" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":20011,"count":1},{"id":21011,"count":1}]}</t>
-        </is>
+      <c r="E298" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":20011,"count":1},{"id":21011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="299">
@@ -6728,10 +6134,8 @@
       <c r="D299" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E299" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":11011,"count":1},{"id":12011,"count":1}]}</t>
-        </is>
+      <c r="E299" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":11011,"count":1},{"id":12011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="300">
@@ -6749,10 +6153,8 @@
       <c r="D300" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E300" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":13011,"count":1},{"id":14011,"count":1}]}</t>
-        </is>
+      <c r="E300" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":13011,"count":1},{"id":14011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="301">
@@ -6770,10 +6172,8 @@
       <c r="D301" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E301" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":15011,"count":1},{"id":16011,"count":1}]}</t>
-        </is>
+      <c r="E301" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":15011,"count":1},{"id":16011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="302">
@@ -6791,10 +6191,8 @@
       <c r="D302" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E302" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":23011,"count":1},{"id":24011,"count":1}]}</t>
-        </is>
+      <c r="E302" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":23011,"count":1},{"id":24011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="303">
@@ -6812,10 +6210,8 @@
       <c r="D303" s="3" t="n">
         <v>573471</v>
       </c>
-      <c r="E303" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":17011,"count":1},{"id":18011,"count":1}]}</t>
-        </is>
+      <c r="E303" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":17011,"count":1},{"id":18011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="304">
@@ -6833,10 +6229,8 @@
       <c r="D304" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E304" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":19}],"items":[{"id":19011,"count":1},{"id":20011,"count":1}]}</t>
-        </is>
+      <c r="E304" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":19}],"items":[{"id":19011,"count":1},{"id":20011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="305">
@@ -6854,10 +6248,8 @@
       <c r="D305" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E305" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":21011,"count":1},{"id":11011,"count":1}]}</t>
-        </is>
+      <c r="E305" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":21011,"count":1},{"id":11011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="306">
@@ -6875,10 +6267,8 @@
       <c r="D306" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E306" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":12011,"count":1},{"id":13011,"count":1}]}</t>
-        </is>
+      <c r="E306" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":12011,"count":1},{"id":13011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="307">
@@ -6896,10 +6286,8 @@
       <c r="D307" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E307" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":19}],"items":[{"id":14011,"count":1},{"id":15011,"count":1}]}</t>
-        </is>
+      <c r="E307" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":19}],"items":[{"id":14011,"count":1},{"id":15011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="308">
@@ -6917,10 +6305,8 @@
       <c r="D308" s="3" t="n">
         <v>573471</v>
       </c>
-      <c r="E308" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":16011,"count":1},{"id":23011,"count":1}]}</t>
-        </is>
+      <c r="E308" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":16011,"count":1},{"id":23011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="309">
@@ -6938,10 +6324,8 @@
       <c r="D309" s="3" t="n">
         <v>573471</v>
       </c>
-      <c r="E309" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":24011,"count":1},{"id":17011,"count":1}]}</t>
-        </is>
+      <c r="E309" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":24011,"count":1},{"id":17011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="310">
@@ -6959,10 +6343,8 @@
       <c r="D310" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E310" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":18011,"count":1},{"id":19011,"count":1}]}</t>
-        </is>
+      <c r="E310" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":18011,"count":1},{"id":19011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="311">
@@ -6980,10 +6362,8 @@
       <c r="D311" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E311" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":20011,"count":1},{"id":21011,"count":1}]}</t>
-        </is>
+      <c r="E311" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":20011,"count":1},{"id":21011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="312">
@@ -7001,10 +6381,8 @@
       <c r="D312" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E312" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":11011,"count":1},{"id":12011,"count":1}]}</t>
-        </is>
+      <c r="E312" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":11011,"count":1},{"id":12011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="313">
@@ -7022,10 +6400,8 @@
       <c r="D313" s="3" t="n">
         <v>573471</v>
       </c>
-      <c r="E313" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":13011,"count":1},{"id":14011,"count":1}]}</t>
-        </is>
+      <c r="E313" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":13011,"count":1},{"id":14011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="314">
@@ -7043,10 +6419,8 @@
       <c r="D314" s="3" t="n">
         <v>573471</v>
       </c>
-      <c r="E314" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":15011,"count":1},{"id":16011,"count":1}]}</t>
-        </is>
+      <c r="E314" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":15011,"count":1},{"id":16011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="315">
@@ -7064,10 +6438,8 @@
       <c r="D315" s="3" t="n">
         <v>573471</v>
       </c>
-      <c r="E315" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":23011,"count":1},{"id":24011,"count":1}]}</t>
-        </is>
+      <c r="E315" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":23011,"count":1},{"id":24011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="316">
@@ -7085,10 +6457,8 @@
       <c r="D316" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E316" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":17011,"count":1},{"id":18011,"count":1}]}</t>
-        </is>
+      <c r="E316" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":17011,"count":1},{"id":18011,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="317">
@@ -7106,10 +6476,8 @@
       <c r="D317" s="3" t="n">
         <v>630819</v>
       </c>
-      <c r="E317" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":19011,"count":1},{"id":20012,"count":1}]}</t>
-        </is>
+      <c r="E317" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":19011,"count":1},{"id":20012,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="318">
@@ -7127,10 +6495,8 @@
       <c r="D318" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E318" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":21012,"count":1},{"id":11012,"count":1}]}</t>
-        </is>
+      <c r="E318" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":21012,"count":1},{"id":11012,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="319">
@@ -7148,10 +6514,8 @@
       <c r="D319" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E319" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":12012,"count":1},{"id":13012,"count":1}]}</t>
-        </is>
+      <c r="E319" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":20}],"items":[{"id":12012,"count":1},{"id":13012,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="320">
@@ -7169,10 +6533,8 @@
       <c r="D320" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E320" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":14012,"count":1},{"id":15012,"count":1}]}</t>
-        </is>
+      <c r="E320" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":19}],"items":[{"id":14012,"count":1},{"id":15012,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="321">
@@ -7190,10 +6552,8 @@
       <c r="D321" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E321" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":16012,"count":1},{"id":23012,"count":1}]}</t>
-        </is>
+      <c r="E321" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":16012,"count":1},{"id":23012,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="322">
@@ -7211,10 +6571,8 @@
       <c r="D322" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E322" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":19}],"items":[{"id":24012,"count":1},{"id":17012,"count":1}]}</t>
-        </is>
+      <c r="E322" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":266},{"token":3,"amount":19}],"items":[{"id":24012,"count":1},{"id":17012,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="323">
@@ -7232,10 +6590,8 @@
       <c r="D323" s="3" t="n">
         <v>700910</v>
       </c>
-      <c r="E323" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":18012,"count":1},{"id":19012,"count":1}]}</t>
-        </is>
+      <c r="E323" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":267},{"token":3,"amount":20}],"items":[{"id":18012,"count":1},{"id":19012,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="324">
@@ -7253,10 +6609,8 @@
       <c r="D324" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E324" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":11013,"count":1},{"id":12013,"count":1}]}</t>
-        </is>
+      <c r="E324" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":11013,"count":1},{"id":12013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="325">
@@ -7274,10 +6628,8 @@
       <c r="D325" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E325" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":13013,"count":1},{"id":14013,"count":1}]}</t>
-        </is>
+      <c r="E325" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":13013,"count":1},{"id":14013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="326">
@@ -7295,10 +6647,8 @@
       <c r="D326" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E326" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":15013,"count":1},{"id":16013,"count":1}]}</t>
-        </is>
+      <c r="E326" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":15013,"count":1},{"id":16013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="327">
@@ -7316,10 +6666,8 @@
       <c r="D327" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E327" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":23013,"count":1},{"id":24013,"count":1}]}</t>
-        </is>
+      <c r="E327" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":23013,"count":1},{"id":24013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="328">
@@ -7337,10 +6685,8 @@
       <c r="D328" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E328" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":17013,"count":1},{"id":18013,"count":1}]}</t>
-        </is>
+      <c r="E328" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":17013,"count":1},{"id":18013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="329">
@@ -7358,10 +6704,8 @@
       <c r="D329" s="3" t="n">
         <v>28476169</v>
       </c>
-      <c r="E329" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":19013,"count":1},{"id":20013,"count":1}]}</t>
-        </is>
+      <c r="E329" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":19013,"count":1},{"id":20013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="330">
@@ -7379,10 +6723,8 @@
       <c r="D330" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E330" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":21013,"count":1},{"id":11013,"count":1}]}</t>
-        </is>
+      <c r="E330" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":21013,"count":1},{"id":11013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="331">
@@ -7400,10 +6742,8 @@
       <c r="D331" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E331" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":12013,"count":1},{"id":13013,"count":1}]}</t>
-        </is>
+      <c r="E331" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":12013,"count":1},{"id":13013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="332">
@@ -7421,10 +6761,8 @@
       <c r="D332" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E332" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":14013,"count":1},{"id":15013,"count":1}]}</t>
-        </is>
+      <c r="E332" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":14013,"count":1},{"id":15013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="333">
@@ -7442,10 +6780,8 @@
       <c r="D333" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E333" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":16013,"count":1},{"id":23013,"count":1}]}</t>
-        </is>
+      <c r="E333" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":16013,"count":1},{"id":23013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="334">
@@ -7463,10 +6799,8 @@
       <c r="D334" s="3" t="n">
         <v>28476169</v>
       </c>
-      <c r="E334" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":24013,"count":1},{"id":17013,"count":1}]}</t>
-        </is>
+      <c r="E334" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":24013,"count":1},{"id":17013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="335">
@@ -7484,10 +6818,8 @@
       <c r="D335" s="3" t="n">
         <v>28476169</v>
       </c>
-      <c r="E335" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":18013,"count":1},{"id":19013,"count":1}]}</t>
-        </is>
+      <c r="E335" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":18013,"count":1},{"id":19013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="336">
@@ -7505,10 +6837,8 @@
       <c r="D336" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E336" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":20013,"count":1},{"id":21013,"count":1}]}</t>
-        </is>
+      <c r="E336" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":20013,"count":1},{"id":21013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="337">
@@ -7526,10 +6856,8 @@
       <c r="D337" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E337" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":88},{"token":3,"amount":18}],"items":[{"id":11013,"count":1},{"id":12013,"count":1}]}</t>
-        </is>
+      <c r="E337" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":88},{"token":3,"amount":18}],"items":[{"id":11013,"count":1},{"id":12013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="338">
@@ -7547,10 +6875,8 @@
       <c r="D338" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E338" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":13013,"count":1},{"id":14013,"count":1}]}</t>
-        </is>
+      <c r="E338" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":13013,"count":1},{"id":14013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="339">
@@ -7568,10 +6894,8 @@
       <c r="D339" s="3" t="n">
         <v>28476169</v>
       </c>
-      <c r="E339" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":15013,"count":1},{"id":16013,"count":1}]}</t>
-        </is>
+      <c r="E339" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":15013,"count":1},{"id":16013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="340">
@@ -7589,10 +6913,8 @@
       <c r="D340" s="3" t="n">
         <v>28476169</v>
       </c>
-      <c r="E340" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":23013,"count":1},{"id":24013,"count":1}]}</t>
-        </is>
+      <c r="E340" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":23013,"count":1},{"id":24013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="341">
@@ -7610,10 +6932,8 @@
       <c r="D341" s="3" t="n">
         <v>28476169</v>
       </c>
-      <c r="E341" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":17013,"count":1},{"id":18013,"count":1}]}</t>
-        </is>
+      <c r="E341" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":17013,"count":1},{"id":18013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="342">
@@ -7631,10 +6951,8 @@
       <c r="D342" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E342" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":19013,"count":1},{"id":20013,"count":1}]}</t>
-        </is>
+      <c r="E342" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":19013,"count":1},{"id":20013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="343">
@@ -7652,10 +6970,8 @@
       <c r="D343" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E343" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":21013,"count":1},{"id":11013,"count":1}]}</t>
-        </is>
+      <c r="E343" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":21013,"count":1},{"id":11013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="344">
@@ -7673,10 +6989,8 @@
       <c r="D344" s="3" t="n">
         <v>28476169</v>
       </c>
-      <c r="E344" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":12013,"count":1},{"id":13013,"count":1}]}</t>
-        </is>
+      <c r="E344" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":12013,"count":1},{"id":13013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="345">
@@ -7694,10 +7008,8 @@
       <c r="D345" s="3" t="n">
         <v>28476169</v>
       </c>
-      <c r="E345" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":14013,"count":1},{"id":15013,"count":1}]}</t>
-        </is>
+      <c r="E345" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":14013,"count":1},{"id":15013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="346">
@@ -7715,10 +7027,8 @@
       <c r="D346" s="3" t="n">
         <v>28476169</v>
       </c>
-      <c r="E346" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":16013,"count":1},{"id":23013,"count":1}]}</t>
-        </is>
+      <c r="E346" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":16013,"count":1},{"id":23013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="347">
@@ -7736,10 +7046,8 @@
       <c r="D347" s="3" t="n">
         <v>28476169</v>
       </c>
-      <c r="E347" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":24013,"count":1},{"id":17013,"count":1}]}</t>
-        </is>
+      <c r="E347" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":24013,"count":1},{"id":17013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="348">
@@ -7757,10 +7065,8 @@
       <c r="D348" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E348" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":18013,"count":1},{"id":19013,"count":1}]}</t>
-        </is>
+      <c r="E348" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":18013,"count":1},{"id":19013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="349">
@@ -7778,10 +7084,8 @@
       <c r="D349" s="3" t="n">
         <v>28476169</v>
       </c>
-      <c r="E349" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":20013,"count":1},{"id":21013,"count":1}]}</t>
-        </is>
+      <c r="E349" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":20013,"count":1},{"id":21013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="350">
@@ -7799,10 +7103,8 @@
       <c r="D350" s="3" t="n">
         <v>28476169</v>
       </c>
-      <c r="E350" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":11013,"count":1},{"id":12013,"count":1}]}</t>
-        </is>
+      <c r="E350" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":11013,"count":1},{"id":12013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="351">
@@ -7820,10 +7122,8 @@
       <c r="D351" s="3" t="n">
         <v>28476169</v>
       </c>
-      <c r="E351" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":13013,"count":1},{"id":14013,"count":1}]}</t>
-        </is>
+      <c r="E351" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":13013,"count":1},{"id":14013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="352">
@@ -7841,10 +7141,8 @@
       <c r="D352" s="3" t="n">
         <v>28476169</v>
       </c>
-      <c r="E352" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":15013,"count":1},{"id":16013,"count":1}]}</t>
-        </is>
+      <c r="E352" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":15013,"count":1},{"id":16013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="353">
@@ -7862,10 +7160,8 @@
       <c r="D353" s="3" t="n">
         <v>28476169</v>
       </c>
-      <c r="E353" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":23013,"count":1},{"id":24013,"count":1}]}</t>
-        </is>
+      <c r="E353" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":23013,"count":1},{"id":24013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="354">
@@ -7883,10 +7179,8 @@
       <c r="D354" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E354" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":17013,"count":1},{"id":18013,"count":1}]}</t>
-        </is>
+      <c r="E354" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":17013,"count":1},{"id":18013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="355">
@@ -7904,10 +7198,8 @@
       <c r="D355" s="3" t="n">
         <v>34171403</v>
       </c>
-      <c r="E355" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":19013,"count":1},{"id":20013,"count":1}]}</t>
-        </is>
+      <c r="E355" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":19013,"count":1},{"id":20013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="356">
@@ -7925,10 +7217,8 @@
       <c r="D356" s="3" t="n">
         <v>34171403</v>
       </c>
-      <c r="E356" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":21013,"count":1},{"id":11013,"count":1}]}</t>
-        </is>
+      <c r="E356" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":21013,"count":1},{"id":11013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="357">
@@ -7946,10 +7236,8 @@
       <c r="D357" s="3" t="n">
         <v>34171403</v>
       </c>
-      <c r="E357" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":12013,"count":1},{"id":13013,"count":1}]}</t>
-        </is>
+      <c r="E357" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":12013,"count":1},{"id":13013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="358">
@@ -7967,10 +7255,8 @@
       <c r="D358" s="3" t="n">
         <v>34171403</v>
       </c>
-      <c r="E358" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":14013,"count":1},{"id":15013,"count":1}]}</t>
-        </is>
+      <c r="E358" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":14013,"count":1},{"id":15013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="359">
@@ -7988,10 +7274,8 @@
       <c r="D359" s="3" t="n">
         <v>34171403</v>
       </c>
-      <c r="E359" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":16013,"count":1},{"id":23013,"count":1}]}</t>
-        </is>
+      <c r="E359" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":16013,"count":1},{"id":23013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="360">
@@ -8009,10 +7293,8 @@
       <c r="D360" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E360" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":24013,"count":1},{"id":17013,"count":1}]}</t>
-        </is>
+      <c r="E360" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":24013,"count":1},{"id":17013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="361">
@@ -8030,10 +7312,8 @@
       <c r="D361" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E361" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":18013,"count":1},{"id":19013,"count":1}]}</t>
-        </is>
+      <c r="E361" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":18013,"count":1},{"id":19013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="362">
@@ -8051,10 +7331,8 @@
       <c r="D362" s="3" t="n">
         <v>34171403</v>
       </c>
-      <c r="E362" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":20013,"count":1},{"id":21013,"count":1}]}</t>
-        </is>
+      <c r="E362" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":20013,"count":1},{"id":21013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="363">
@@ -8072,10 +7350,8 @@
       <c r="D363" s="3" t="n">
         <v>34171403</v>
       </c>
-      <c r="E363" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":11013,"count":1},{"id":12013,"count":1}]}</t>
-        </is>
+      <c r="E363" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":11013,"count":1},{"id":12013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="364">
@@ -8093,10 +7369,8 @@
       <c r="D364" s="3" t="n">
         <v>34171403</v>
       </c>
-      <c r="E364" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":88},{"token":3,"amount":18}],"items":[{"id":13013,"count":1},{"id":14013,"count":1}]}</t>
-        </is>
+      <c r="E364" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":88},{"token":3,"amount":18}],"items":[{"id":13013,"count":1},{"id":14013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="365">
@@ -8114,10 +7388,8 @@
       <c r="D365" s="3" t="n">
         <v>34171403</v>
       </c>
-      <c r="E365" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":15013,"count":1},{"id":16013,"count":1}]}</t>
-        </is>
+      <c r="E365" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":15013,"count":1},{"id":16013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="366">
@@ -8135,10 +7407,8 @@
       <c r="D366" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E366" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":23013,"count":1},{"id":24013,"count":1}]}</t>
-        </is>
+      <c r="E366" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":23013,"count":1},{"id":24013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="367">
@@ -8156,10 +7426,8 @@
       <c r="D367" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E367" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":17013,"count":1},{"id":18013,"count":1}]}</t>
-        </is>
+      <c r="E367" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":17013,"count":1},{"id":18013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="368">
@@ -8177,10 +7445,8 @@
       <c r="D368" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E368" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":19013,"count":1},{"id":20013,"count":1}]}</t>
-        </is>
+      <c r="E368" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":19013,"count":1},{"id":20013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="369">
@@ -8198,10 +7464,8 @@
       <c r="D369" s="3" t="n">
         <v>34171403</v>
       </c>
-      <c r="E369" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":21013,"count":1},{"id":11013,"count":1}]}</t>
-        </is>
+      <c r="E369" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":21013,"count":1},{"id":11013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="370">
@@ -8219,10 +7483,8 @@
       <c r="D370" s="3" t="n">
         <v>34171403</v>
       </c>
-      <c r="E370" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":12013,"count":1},{"id":13013,"count":1}]}</t>
-        </is>
+      <c r="E370" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":12013,"count":1},{"id":13013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="371">
@@ -8240,10 +7502,8 @@
       <c r="D371" s="3" t="n">
         <v>34171403</v>
       </c>
-      <c r="E371" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":14013,"count":1},{"id":15013,"count":1}]}</t>
-        </is>
+      <c r="E371" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":14013,"count":1},{"id":15013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="372">
@@ -8261,10 +7521,8 @@
       <c r="D372" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E372" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":16013,"count":1},{"id":23013,"count":1}]}</t>
-        </is>
+      <c r="E372" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":16013,"count":1},{"id":23013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="373">
@@ -8282,10 +7540,8 @@
       <c r="D373" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E373" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":24013,"count":1},{"id":17013,"count":1}]}</t>
-        </is>
+      <c r="E373" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":24013,"count":1},{"id":17013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="374">
@@ -8303,10 +7559,8 @@
       <c r="D374" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E374" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":18013,"count":1},{"id":19013,"count":1}]}</t>
-        </is>
+      <c r="E374" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":18013,"count":1},{"id":19013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="375">
@@ -8324,10 +7578,8 @@
       <c r="D375" s="3" t="n">
         <v>31064912</v>
       </c>
-      <c r="E375" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":20013,"count":1},{"id":21013,"count":1}]}</t>
-        </is>
+      <c r="E375" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":20013,"count":1},{"id":21013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="376">
@@ -8345,10 +7597,8 @@
       <c r="D376" s="3" t="n">
         <v>34171403</v>
       </c>
-      <c r="E376" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":11013,"count":1},{"id":12013,"count":1}]}</t>
-        </is>
+      <c r="E376" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":18}],"items":[{"id":11013,"count":1},{"id":12013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="377">
@@ -8366,10 +7616,8 @@
       <c r="D377" s="3" t="n">
         <v>34171403</v>
       </c>
-      <c r="E377" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":13013,"count":1},{"id":14013,"count":1}]}</t>
-        </is>
+      <c r="E377" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":87},{"token":3,"amount":19}],"items":[{"id":13013,"count":1},{"id":14013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="378">
@@ -8387,10 +7635,8 @@
       <c r="D378" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E378" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":11013,"count":1},{"id":12013,"count":1}]}</t>
-        </is>
+      <c r="E378" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":11013,"count":1},{"id":12013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="379">
@@ -8408,10 +7654,8 @@
       <c r="D379" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E379" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":13013,"count":1},{"id":14013,"count":1}]}</t>
-        </is>
+      <c r="E379" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":13013,"count":1},{"id":14013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="380">
@@ -8429,10 +7673,8 @@
       <c r="D380" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E380" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":15013,"count":1},{"id":16013,"count":1}]}</t>
-        </is>
+      <c r="E380" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":15013,"count":1},{"id":16013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="381">
@@ -8450,10 +7692,8 @@
       <c r="D381" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E381" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":23013,"count":1},{"id":24013,"count":1}]}</t>
-        </is>
+      <c r="E381" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":23013,"count":1},{"id":24013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="382">
@@ -8471,10 +7711,8 @@
       <c r="D382" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E382" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":17013,"count":1},{"id":18013,"count":1}]}</t>
-        </is>
+      <c r="E382" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":17013,"count":1},{"id":18013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="383">
@@ -8492,10 +7730,8 @@
       <c r="D383" s="3" t="n">
         <v>33135906</v>
       </c>
-      <c r="E383" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":19013,"count":1},{"id":20013,"count":1}]}</t>
-        </is>
+      <c r="E383" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":19013,"count":1},{"id":20013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="384">
@@ -8513,10 +7749,8 @@
       <c r="D384" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E384" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":21013,"count":1},{"id":11013,"count":1}]}</t>
-        </is>
+      <c r="E384" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":21013,"count":1},{"id":11013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="385">
@@ -8534,10 +7768,8 @@
       <c r="D385" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E385" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":12013,"count":1},{"id":13013,"count":1}]}</t>
-        </is>
+      <c r="E385" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":12013,"count":1},{"id":13013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="386">
@@ -8555,10 +7787,8 @@
       <c r="D386" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E386" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":14013,"count":1},{"id":15013,"count":1}]}</t>
-        </is>
+      <c r="E386" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":14013,"count":1},{"id":15013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="387">
@@ -8576,10 +7806,8 @@
       <c r="D387" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E387" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":16013,"count":1},{"id":23013,"count":1}]}</t>
-        </is>
+      <c r="E387" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":16013,"count":1},{"id":23013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="388">
@@ -8597,10 +7825,8 @@
       <c r="D388" s="3" t="n">
         <v>33135906</v>
       </c>
-      <c r="E388" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":24013,"count":1},{"id":17013,"count":1}]}</t>
-        </is>
+      <c r="E388" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":24013,"count":1},{"id":17013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="389">
@@ -8618,10 +7844,8 @@
       <c r="D389" s="3" t="n">
         <v>33135906</v>
       </c>
-      <c r="E389" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":18013,"count":1},{"id":19013,"count":1}]}</t>
-        </is>
+      <c r="E389" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":18013,"count":1},{"id":19013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="390">
@@ -8639,10 +7863,8 @@
       <c r="D390" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E390" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":20013,"count":1},{"id":21013,"count":1}]}</t>
-        </is>
+      <c r="E390" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":20013,"count":1},{"id":21013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="391">
@@ -8660,10 +7882,8 @@
       <c r="D391" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E391" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":11013,"count":1},{"id":12013,"count":1}]}</t>
-        </is>
+      <c r="E391" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":11013,"count":1},{"id":12013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="392">
@@ -8681,10 +7901,8 @@
       <c r="D392" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E392" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":13013,"count":1},{"id":14013,"count":1}]}</t>
-        </is>
+      <c r="E392" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":13013,"count":1},{"id":14013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="393">
@@ -8702,10 +7920,8 @@
       <c r="D393" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E393" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":15013,"count":1},{"id":16013,"count":1}]}</t>
-        </is>
+      <c r="E393" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":15013,"count":1},{"id":16013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="394">
@@ -8723,10 +7939,8 @@
       <c r="D394" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E394" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":23013,"count":1},{"id":24013,"count":1}]}</t>
-        </is>
+      <c r="E394" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":23013,"count":1},{"id":24013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="395">
@@ -8744,10 +7958,8 @@
       <c r="D395" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E395" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":17013,"count":1},{"id":18013,"count":1}]}</t>
-        </is>
+      <c r="E395" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":17013,"count":1},{"id":18013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="396">
@@ -8765,10 +7977,8 @@
       <c r="D396" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E396" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":19013,"count":1},{"id":20013,"count":1}]}</t>
-        </is>
+      <c r="E396" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":19013,"count":1},{"id":20013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="397">
@@ -8786,10 +7996,8 @@
       <c r="D397" s="3" t="n">
         <v>44181208</v>
       </c>
-      <c r="E397" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":21013,"count":1},{"id":11013,"count":1}]}</t>
-        </is>
+      <c r="E397" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":21013,"count":1},{"id":11013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="398">
@@ -8807,10 +8015,8 @@
       <c r="D398" s="3" t="n">
         <v>44181208</v>
       </c>
-      <c r="E398" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":12013,"count":1},{"id":13013,"count":1}]}</t>
-        </is>
+      <c r="E398" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":12013,"count":1},{"id":13013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="399">
@@ -8828,10 +8034,8 @@
       <c r="D399" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E399" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":14014,"count":1},{"id":15013,"count":1}]}</t>
-        </is>
+      <c r="E399" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":14014,"count":1},{"id":15013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="400">
@@ -8849,10 +8053,8 @@
       <c r="D400" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E400" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":16013,"count":1},{"id":23013,"count":1}]}</t>
-        </is>
+      <c r="E400" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":16013,"count":1},{"id":23013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="401">
@@ -8870,10 +8072,8 @@
       <c r="D401" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E401" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":24013,"count":1},{"id":17013,"count":1}]}</t>
-        </is>
+      <c r="E401" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":24013,"count":1},{"id":17013,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="402">
@@ -8891,10 +8091,8 @@
       <c r="D402" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E402" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":18013,"count":1},{"id":19014,"count":1}]}</t>
-        </is>
+      <c r="E402" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":18013,"count":1},{"id":19014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="403">
@@ -8912,10 +8110,8 @@
       <c r="D403" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E403" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":20014,"count":1},{"id":21014,"count":1}]}</t>
-        </is>
+      <c r="E403" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":20014,"count":1},{"id":21014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="404">
@@ -8933,10 +8129,8 @@
       <c r="D404" s="3" t="n">
         <v>44181208</v>
       </c>
-      <c r="E404" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":11014,"count":1},{"id":12014,"count":1}]}</t>
-        </is>
+      <c r="E404" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":11014,"count":1},{"id":12014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="405">
@@ -8954,10 +8148,8 @@
       <c r="D405" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E405" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":13014,"count":1},{"id":14014,"count":1}]}</t>
-        </is>
+      <c r="E405" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":13014,"count":1},{"id":14014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="406">
@@ -8975,10 +8167,8 @@
       <c r="D406" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E406" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":15014,"count":1},{"id":16014,"count":1}]}</t>
-        </is>
+      <c r="E406" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":15014,"count":1},{"id":16014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="407">
@@ -8996,10 +8186,8 @@
       <c r="D407" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E407" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":23014,"count":1},{"id":24014,"count":1}]}</t>
-        </is>
+      <c r="E407" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":23014,"count":1},{"id":24014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="408">
@@ -9017,10 +8205,8 @@
       <c r="D408" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E408" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":17014,"count":1},{"id":18014,"count":1}]}</t>
-        </is>
+      <c r="E408" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":17014,"count":1},{"id":18014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="409">
@@ -9038,10 +8224,8 @@
       <c r="D409" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E409" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":19014,"count":1},{"id":20014,"count":1}]}</t>
-        </is>
+      <c r="E409" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":19014,"count":1},{"id":20014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="410">
@@ -9059,10 +8243,8 @@
       <c r="D410" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E410" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":21014,"count":1},{"id":11014,"count":1}]}</t>
-        </is>
+      <c r="E410" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":21014,"count":1},{"id":11014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="411">
@@ -9080,10 +8262,8 @@
       <c r="D411" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E411" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":12014,"count":1},{"id":13014,"count":1}]}</t>
-        </is>
+      <c r="E411" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":12014,"count":1},{"id":13014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="412">
@@ -9101,10 +8281,8 @@
       <c r="D412" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E412" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":14014,"count":1},{"id":15014,"count":1}]}</t>
-        </is>
+      <c r="E412" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":14014,"count":1},{"id":15014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="413">
@@ -9122,10 +8300,8 @@
       <c r="D413" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E413" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":16014,"count":1},{"id":23014,"count":1}]}</t>
-        </is>
+      <c r="E413" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":16014,"count":1},{"id":23014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="414">
@@ -9143,10 +8319,8 @@
       <c r="D414" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E414" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":24014,"count":1},{"id":17014,"count":1}]}</t>
-        </is>
+      <c r="E414" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":24014,"count":1},{"id":17014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="415">
@@ -9164,10 +8338,8 @@
       <c r="D415" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E415" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":18014,"count":1},{"id":19014,"count":1}]}</t>
-        </is>
+      <c r="E415" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":18014,"count":1},{"id":19014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="416">
@@ -9185,10 +8357,8 @@
       <c r="D416" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E416" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":20014,"count":1},{"id":21014,"count":1}]}</t>
-        </is>
+      <c r="E416" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":20014,"count":1},{"id":21014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="417">
@@ -9206,10 +8376,8 @@
       <c r="D417" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E417" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":11014,"count":1},{"id":12014,"count":1}]}</t>
-        </is>
+      <c r="E417" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":11014,"count":1},{"id":12014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="418">
@@ -9227,10 +8395,8 @@
       <c r="D418" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E418" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":13014,"count":1},{"id":14014,"count":1}]}</t>
-        </is>
+      <c r="E418" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":13014,"count":1},{"id":14014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="419">
@@ -9248,10 +8414,8 @@
       <c r="D419" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E419" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":15014,"count":1},{"id":16014,"count":1}]}</t>
-        </is>
+      <c r="E419" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":15014,"count":1},{"id":16014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="420">
@@ -9269,10 +8433,8 @@
       <c r="D420" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E420" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":23014,"count":1},{"id":24014,"count":1}]}</t>
-        </is>
+      <c r="E420" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":23014,"count":1},{"id":24014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="421">
@@ -9290,10 +8452,8 @@
       <c r="D421" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E421" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":17014,"count":1},{"id":18014,"count":1}]}</t>
-        </is>
+      <c r="E421" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":17014,"count":1},{"id":18014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="422">
@@ -9311,10 +8471,8 @@
       <c r="D422" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E422" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":19014,"count":1},{"id":20014,"count":1}]}</t>
-        </is>
+      <c r="E422" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":19014,"count":1},{"id":20014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="423">
@@ -9332,10 +8490,8 @@
       <c r="D423" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E423" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":21014,"count":1},{"id":11014,"count":1}]}</t>
-        </is>
+      <c r="E423" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":21014,"count":1},{"id":11014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="424">
@@ -9353,10 +8509,8 @@
       <c r="D424" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E424" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":12014,"count":1},{"id":13014,"count":1}]}</t>
-        </is>
+      <c r="E424" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":12014,"count":1},{"id":13014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="425">
@@ -9374,10 +8528,8 @@
       <c r="D425" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E425" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":14014,"count":1},{"id":15014,"count":1}]}</t>
-        </is>
+      <c r="E425" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":14014,"count":1},{"id":15014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="426">
@@ -9395,10 +8547,8 @@
       <c r="D426" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E426" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":16014,"count":1},{"id":23014,"count":1}]}</t>
-        </is>
+      <c r="E426" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":16014,"count":1},{"id":23014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="427">
@@ -9416,10 +8566,8 @@
       <c r="D427" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E427" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":24014,"count":1},{"id":17014,"count":1}]}</t>
-        </is>
+      <c r="E427" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":24014,"count":1},{"id":17014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="428">
@@ -9437,10 +8585,8 @@
       <c r="D428" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E428" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":18014,"count":1},{"id":19014,"count":1}]}</t>
-        </is>
+      <c r="E428" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":18014,"count":1},{"id":19014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="429">
@@ -9458,10 +8604,8 @@
       <c r="D429" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E429" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":20014,"count":1},{"id":21014,"count":1}]}</t>
-        </is>
+      <c r="E429" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":20014,"count":1},{"id":21014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="430">
@@ -9479,10 +8623,8 @@
       <c r="D430" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E430" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":11014,"count":1},{"id":12014,"count":1}]}</t>
-        </is>
+      <c r="E430" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":18}],"items":[{"id":11014,"count":1},{"id":12014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="431">
@@ -9500,10 +8642,8 @@
       <c r="D431" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E431" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":13014,"count":1},{"id":14014,"count":1}]}</t>
-        </is>
+      <c r="E431" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":17}],"items":[{"id":13014,"count":1},{"id":14014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="432">
@@ -9521,10 +8661,8 @@
       <c r="D432" s="3" t="n">
         <v>36148261</v>
       </c>
-      <c r="E432" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":15014,"count":1},{"id":16014,"count":1}]}</t>
-        </is>
+      <c r="E432" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":15014,"count":1},{"id":16014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="433">
@@ -9542,10 +8680,8 @@
       <c r="D433" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E433" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":23014,"count":1},{"id":24014,"count":1}]}</t>
-        </is>
+      <c r="E433" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":241},{"token":3,"amount":17}],"items":[{"id":23014,"count":1},{"id":24014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="434">
@@ -9563,10 +8699,8 @@
       <c r="D434" s="3" t="n">
         <v>39763087</v>
       </c>
-      <c r="E434" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":17014,"count":1},{"id":18014,"count":1}]}</t>
-        </is>
+      <c r="E434" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":240},{"token":3,"amount":18}],"items":[{"id":17014,"count":1},{"id":18014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="435">
@@ -9584,10 +8718,8 @@
       <c r="D435" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E435" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":11014,"count":1},{"id":12014,"count":1}]}</t>
-        </is>
+      <c r="E435" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":11014,"count":1},{"id":12014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="436">
@@ -9605,10 +8737,8 @@
       <c r="D436" s="3" t="n">
         <v>46942534</v>
       </c>
-      <c r="E436" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":13014,"count":1},{"id":14014,"count":1}]}</t>
-        </is>
+      <c r="E436" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":13014,"count":1},{"id":14014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="437">
@@ -9626,10 +8756,8 @@
       <c r="D437" s="3" t="n">
         <v>46942534</v>
       </c>
-      <c r="E437" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":15014,"count":1},{"id":16014,"count":1}]}</t>
-        </is>
+      <c r="E437" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":15014,"count":1},{"id":16014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="438">
@@ -9647,10 +8775,8 @@
       <c r="D438" s="3" t="n">
         <v>46942534</v>
       </c>
-      <c r="E438" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":23014,"count":1},{"id":24014,"count":1}]}</t>
-        </is>
+      <c r="E438" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":23014,"count":1},{"id":24014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="439">
@@ -9668,10 +8794,8 @@
       <c r="D439" s="3" t="n">
         <v>46942534</v>
       </c>
-      <c r="E439" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":17014,"count":1},{"id":18014,"count":1}]}</t>
-        </is>
+      <c r="E439" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":17014,"count":1},{"id":18014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="440">
@@ -9689,10 +8813,8 @@
       <c r="D440" s="3" t="n">
         <v>46942534</v>
       </c>
-      <c r="E440" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":19014,"count":1},{"id":20014,"count":1}]}</t>
-        </is>
+      <c r="E440" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":19014,"count":1},{"id":20014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="441">
@@ -9710,10 +8832,8 @@
       <c r="D441" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E441" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":21014,"count":1},{"id":11014,"count":1}]}</t>
-        </is>
+      <c r="E441" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":21014,"count":1},{"id":11014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="442">
@@ -9731,10 +8851,8 @@
       <c r="D442" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E442" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":12014,"count":1},{"id":13014,"count":1}]}</t>
-        </is>
+      <c r="E442" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":12014,"count":1},{"id":13014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="443">
@@ -9752,10 +8870,8 @@
       <c r="D443" s="3" t="n">
         <v>46942534</v>
       </c>
-      <c r="E443" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":14014,"count":1},{"id":15014,"count":1}]}</t>
-        </is>
+      <c r="E443" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":14014,"count":1},{"id":15014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="444">
@@ -9773,10 +8889,8 @@
       <c r="D444" s="3" t="n">
         <v>46942534</v>
       </c>
-      <c r="E444" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":16014,"count":1},{"id":23014,"count":1}]}</t>
-        </is>
+      <c r="E444" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":16014,"count":1},{"id":23014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="445">
@@ -9794,10 +8908,8 @@
       <c r="D445" s="3" t="n">
         <v>46942534</v>
       </c>
-      <c r="E445" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":24014,"count":1},{"id":17014,"count":1}]}</t>
-        </is>
+      <c r="E445" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":24014,"count":1},{"id":17014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="446">
@@ -9815,10 +8927,8 @@
       <c r="D446" s="3" t="n">
         <v>46942534</v>
       </c>
-      <c r="E446" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":18014,"count":1},{"id":19014,"count":1}]}</t>
-        </is>
+      <c r="E446" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":18014,"count":1},{"id":19014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="447">
@@ -9836,10 +8946,8 @@
       <c r="D447" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E447" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":20014,"count":1},{"id":21014,"count":1}]}</t>
-        </is>
+      <c r="E447" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":20014,"count":1},{"id":21014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="448">
@@ -9857,10 +8965,8 @@
       <c r="D448" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E448" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":11014,"count":1},{"id":12014,"count":1}]}</t>
-        </is>
+      <c r="E448" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":11014,"count":1},{"id":12014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="449">
@@ -9878,10 +8984,8 @@
       <c r="D449" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E449" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":13014,"count":1},{"id":14014,"count":1}]}</t>
-        </is>
+      <c r="E449" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":13014,"count":1},{"id":14014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="450">
@@ -9899,10 +9003,8 @@
       <c r="D450" s="3" t="n">
         <v>46942534</v>
       </c>
-      <c r="E450" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":15014,"count":1},{"id":16014,"count":1}]}</t>
-        </is>
+      <c r="E450" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":15014,"count":1},{"id":16014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="451">
@@ -9920,10 +9022,8 @@
       <c r="D451" s="3" t="n">
         <v>46942534</v>
       </c>
-      <c r="E451" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":23014,"count":1},{"id":24014,"count":1}]}</t>
-        </is>
+      <c r="E451" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":23014,"count":1},{"id":24014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="452">
@@ -9941,10 +9041,8 @@
       <c r="D452" s="3" t="n">
         <v>46942534</v>
       </c>
-      <c r="E452" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":17014,"count":1},{"id":18014,"count":1}]}</t>
-        </is>
+      <c r="E452" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":17014,"count":1},{"id":18014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="453">
@@ -9962,10 +9060,8 @@
       <c r="D453" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E453" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":19014,"count":1},{"id":20014,"count":1}]}</t>
-        </is>
+      <c r="E453" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":19014,"count":1},{"id":20014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="454">
@@ -9983,10 +9079,8 @@
       <c r="D454" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E454" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":21014,"count":1},{"id":11014,"count":1}]}</t>
-        </is>
+      <c r="E454" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":21014,"count":1},{"id":11014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="455">
@@ -10004,10 +9098,8 @@
       <c r="D455" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E455" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":12014,"count":1},{"id":13014,"count":1}]}</t>
-        </is>
+      <c r="E455" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":12014,"count":1},{"id":13014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="456">
@@ -10025,10 +9117,8 @@
       <c r="D456" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E456" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":14014,"count":1},{"id":15014,"count":1}]}</t>
-        </is>
+      <c r="E456" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":14014,"count":1},{"id":15014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="457">
@@ -10046,10 +9136,8 @@
       <c r="D457" s="3" t="n">
         <v>46942534</v>
       </c>
-      <c r="E457" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":16014,"count":1},{"id":23014,"count":1}]}</t>
-        </is>
+      <c r="E457" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":16014,"count":1},{"id":23014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="458">
@@ -10067,10 +9155,8 @@
       <c r="D458" s="3" t="n">
         <v>46942534</v>
       </c>
-      <c r="E458" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":24014,"count":1},{"id":17014,"count":1}]}</t>
-        </is>
+      <c r="E458" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":24014,"count":1},{"id":17014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="459">
@@ -10088,10 +9174,8 @@
       <c r="D459" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E459" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":18014,"count":1},{"id":19014,"count":1}]}</t>
-        </is>
+      <c r="E459" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":18014,"count":1},{"id":19014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="460">
@@ -10109,10 +9193,8 @@
       <c r="D460" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E460" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":20014,"count":1},{"id":21014,"count":1}]}</t>
-        </is>
+      <c r="E460" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":20014,"count":1},{"id":21014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="461">
@@ -10130,10 +9212,8 @@
       <c r="D461" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E461" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":11014,"count":1},{"id":12014,"count":1}]}</t>
-        </is>
+      <c r="E461" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":11014,"count":1},{"id":12014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="462">
@@ -10151,10 +9231,8 @@
       <c r="D462" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E462" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":13014,"count":1},{"id":14014,"count":1}]}</t>
-        </is>
+      <c r="E462" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":13014,"count":1},{"id":14014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="463">
@@ -10172,10 +9250,8 @@
       <c r="D463" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E463" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":15014,"count":1},{"id":16014,"count":1}]}</t>
-        </is>
+      <c r="E463" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":15014,"count":1},{"id":16014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="464">
@@ -10193,10 +9269,8 @@
       <c r="D464" s="3" t="n">
         <v>46942534</v>
       </c>
-      <c r="E464" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":23014,"count":1},{"id":24014,"count":1}]}</t>
-        </is>
+      <c r="E464" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":23014,"count":1},{"id":24014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="465">
@@ -10214,10 +9288,8 @@
       <c r="D465" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E465" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":17014,"count":1},{"id":18014,"count":1}]}</t>
-        </is>
+      <c r="E465" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":17014,"count":1},{"id":18014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="466">
@@ -10235,10 +9307,8 @@
       <c r="D466" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E466" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":19014,"count":1},{"id":20014,"count":1}]}</t>
-        </is>
+      <c r="E466" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":19014,"count":1},{"id":20014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="467">
@@ -10256,10 +9326,8 @@
       <c r="D467" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E467" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":21014,"count":1},{"id":11014,"count":1}]}</t>
-        </is>
+      <c r="E467" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":21014,"count":1},{"id":11014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="468">
@@ -10277,10 +9345,8 @@
       <c r="D468" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E468" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":12014,"count":1},{"id":13014,"count":1}]}</t>
-        </is>
+      <c r="E468" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":12014,"count":1},{"id":13014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="469">
@@ -10298,10 +9364,8 @@
       <c r="D469" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E469" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":14014,"count":1},{"id":15014,"count":1}]}</t>
-        </is>
+      <c r="E469" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":14014,"count":1},{"id":15014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="470">
@@ -10319,10 +9383,8 @@
       <c r="D470" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E470" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":16014,"count":1},{"id":23014,"count":1}]}</t>
-        </is>
+      <c r="E470" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":16014,"count":1},{"id":23014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="471">
@@ -10340,10 +9402,8 @@
       <c r="D471" s="3" t="n">
         <v>38407528</v>
       </c>
-      <c r="E471" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":24014,"count":1},{"id":17014,"count":1}]}</t>
-        </is>
+      <c r="E471" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":24014,"count":1},{"id":17014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="472">
@@ -10361,10 +9421,8 @@
       <c r="D472" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E472" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":18014,"count":1},{"id":19014,"count":1}]}</t>
-        </is>
+      <c r="E472" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":18014,"count":1},{"id":19014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="473">
@@ -10382,10 +9440,8 @@
       <c r="D473" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E473" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":20014,"count":1},{"id":21014,"count":1}]}</t>
-        </is>
+      <c r="E473" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":20014,"count":1},{"id":21014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="474">
@@ -10403,10 +9459,8 @@
       <c r="D474" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E474" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":11014,"count":1},{"id":12014,"count":1}]}</t>
-        </is>
+      <c r="E474" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":11014,"count":1},{"id":12014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="475">
@@ -10424,10 +9478,8 @@
       <c r="D475" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E475" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":13014,"count":1},{"id":14015,"count":1}]}</t>
-        </is>
+      <c r="E475" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":13014,"count":1},{"id":14015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="476">
@@ -10445,10 +9497,8 @@
       <c r="D476" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E476" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":15014,"count":1},{"id":16014,"count":1}]}</t>
-        </is>
+      <c r="E476" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":15014,"count":1},{"id":16014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="477">
@@ -10466,10 +9516,8 @@
       <c r="D477" s="3" t="n">
         <v>38407528</v>
       </c>
-      <c r="E477" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":23014,"count":1},{"id":24014,"count":1}]}</t>
-        </is>
+      <c r="E477" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":23014,"count":1},{"id":24014,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="478">
@@ -10487,10 +9535,8 @@
       <c r="D478" s="3" t="n">
         <v>38407528</v>
       </c>
-      <c r="E478" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":17014,"count":1},{"id":18015,"count":1}]}</t>
-        </is>
+      <c r="E478" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":17014,"count":1},{"id":18015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="479">
@@ -10508,10 +9554,8 @@
       <c r="D479" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E479" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":19015,"count":1},{"id":20015,"count":1}]}</t>
-        </is>
+      <c r="E479" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":19015,"count":1},{"id":20015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="480">
@@ -10529,10 +9573,8 @@
       <c r="D480" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E480" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":21015,"count":1},{"id":11015,"count":1}]}</t>
-        </is>
+      <c r="E480" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":21015,"count":1},{"id":11015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="481">
@@ -10550,10 +9592,8 @@
       <c r="D481" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E481" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":12015,"count":1},{"id":13015,"count":1}]}</t>
-        </is>
+      <c r="E481" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":12015,"count":1},{"id":13015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="482">
@@ -10571,10 +9611,8 @@
       <c r="D482" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E482" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":14015,"count":1},{"id":15015,"count":1}]}</t>
-        </is>
+      <c r="E482" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":14015,"count":1},{"id":15015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="483">
@@ -10592,10 +9630,8 @@
       <c r="D483" s="3" t="n">
         <v>38407528</v>
       </c>
-      <c r="E483" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":16015,"count":1},{"id":23015,"count":1}]}</t>
-        </is>
+      <c r="E483" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":16015,"count":1},{"id":23015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="484">
@@ -10613,10 +9649,8 @@
       <c r="D484" s="3" t="n">
         <v>38407528</v>
       </c>
-      <c r="E484" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":24015,"count":1},{"id":17015,"count":1}]}</t>
-        </is>
+      <c r="E484" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":24015,"count":1},{"id":17015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="485">
@@ -10634,10 +9668,8 @@
       <c r="D485" s="3" t="n">
         <v>38407528</v>
       </c>
-      <c r="E485" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":18015,"count":1},{"id":19015,"count":1}]}</t>
-        </is>
+      <c r="E485" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":18015,"count":1},{"id":19015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="486">
@@ -10655,10 +9687,8 @@
       <c r="D486" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E486" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":20015,"count":1},{"id":21015,"count":1}]}</t>
-        </is>
+      <c r="E486" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":20015,"count":1},{"id":21015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="487">
@@ -10676,10 +9706,8 @@
       <c r="D487" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E487" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":11015,"count":1},{"id":12015,"count":1}]}</t>
-        </is>
+      <c r="E487" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":11015,"count":1},{"id":12015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="488">
@@ -10697,10 +9725,8 @@
       <c r="D488" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E488" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":13015,"count":1},{"id":14015,"count":1}]}</t>
-        </is>
+      <c r="E488" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":13015,"count":1},{"id":14015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="489">
@@ -10718,10 +9744,8 @@
       <c r="D489" s="3" t="n">
         <v>38407528</v>
       </c>
-      <c r="E489" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":15015,"count":1},{"id":16015,"count":1}]}</t>
-        </is>
+      <c r="E489" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":15015,"count":1},{"id":16015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="490">
@@ -10739,10 +9763,8 @@
       <c r="D490" s="3" t="n">
         <v>38407528</v>
       </c>
-      <c r="E490" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":23015,"count":1},{"id":24015,"count":1}]}</t>
-        </is>
+      <c r="E490" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":23015,"count":1},{"id":24015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="491">
@@ -10760,10 +9782,8 @@
       <c r="D491" s="3" t="n">
         <v>38407528</v>
       </c>
-      <c r="E491" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":17015,"count":1},{"id":18015,"count":1}]}</t>
-        </is>
+      <c r="E491" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":17015,"count":1},{"id":18015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="492">
@@ -10781,10 +9801,8 @@
       <c r="D492" s="3" t="n">
         <v>38407528</v>
       </c>
-      <c r="E492" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":19015,"count":1},{"id":20015,"count":1}]}</t>
-        </is>
+      <c r="E492" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":19015,"count":1},{"id":20015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="493">
@@ -10802,10 +9820,8 @@
       <c r="D493" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E493" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":21015,"count":1},{"id":11015,"count":1}]}</t>
-        </is>
+      <c r="E493" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":516},{"token":3,"amount":16}],"items":[{"id":21015,"count":1},{"id":11015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="494">
@@ -10823,10 +9839,8 @@
       <c r="D494" s="3" t="n">
         <v>42248280</v>
       </c>
-      <c r="E494" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":12015,"count":1},{"id":13015,"count":1}]}</t>
-        </is>
+      <c r="E494" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":517},{"token":3,"amount":17}],"items":[{"id":12015,"count":1},{"id":13015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="495">
@@ -10844,10 +9858,8 @@
       <c r="D495" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E495" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":11015,"count":1},{"id":12015,"count":1}]}</t>
-        </is>
+      <c r="E495" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":11015,"count":1},{"id":12015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="496">
@@ -10865,10 +9877,8 @@
       <c r="D496" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E496" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":13015,"count":1},{"id":14015,"count":1}]}</t>
-        </is>
+      <c r="E496" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":13015,"count":1},{"id":14015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="497">
@@ -10886,10 +9896,8 @@
       <c r="D497" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E497" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":15015,"count":1},{"id":16015,"count":1}]}</t>
-        </is>
+      <c r="E497" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":15015,"count":1},{"id":16015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="498">
@@ -10907,10 +9915,8 @@
       <c r="D498" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E498" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":15}],"items":[{"id":23015,"count":1},{"id":24015,"count":1}]}</t>
-        </is>
+      <c r="E498" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":15}],"items":[{"id":23015,"count":1},{"id":24015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="499">
@@ -10928,10 +9934,8 @@
       <c r="D499" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E499" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":17015,"count":1},{"id":18015,"count":1}]}</t>
-        </is>
+      <c r="E499" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":17015,"count":1},{"id":18015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="500">
@@ -10949,10 +9953,8 @@
       <c r="D500" s="3" t="n">
         <v>12877662</v>
       </c>
-      <c r="E500" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":19015,"count":1},{"id":20015,"count":1}]}</t>
-        </is>
+      <c r="E500" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":19015,"count":1},{"id":20015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="501">
@@ -10970,10 +9972,8 @@
       <c r="D501" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E501" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":21015,"count":1},{"id":11015,"count":1}]}</t>
-        </is>
+      <c r="E501" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":21015,"count":1},{"id":11015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="502">
@@ -10991,10 +9991,8 @@
       <c r="D502" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E502" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":12015,"count":1},{"id":13015,"count":1}]}</t>
-        </is>
+      <c r="E502" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":12015,"count":1},{"id":13015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="503">
@@ -11012,10 +10010,8 @@
       <c r="D503" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E503" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":14015,"count":1},{"id":15015,"count":1}]}</t>
-        </is>
+      <c r="E503" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":14015,"count":1},{"id":15015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="504">
@@ -11033,10 +10029,8 @@
       <c r="D504" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E504" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":16015,"count":1},{"id":23015,"count":1}]}</t>
-        </is>
+      <c r="E504" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":16015,"count":1},{"id":23015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="505">
@@ -11054,10 +10048,8 @@
       <c r="D505" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E505" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":24015,"count":1},{"id":17015,"count":1}]}</t>
-        </is>
+      <c r="E505" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":24015,"count":1},{"id":17015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="506">
@@ -11075,10 +10067,8 @@
       <c r="D506" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E506" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":15}],"items":[{"id":18015,"count":1},{"id":19015,"count":1}]}</t>
-        </is>
+      <c r="E506" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":15}],"items":[{"id":18015,"count":1},{"id":19015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="507">
@@ -11096,10 +10086,8 @@
       <c r="D507" s="3" t="n">
         <v>10731385</v>
       </c>
-      <c r="E507" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":20015,"count":1},{"id":21015,"count":1}]}</t>
-        </is>
+      <c r="E507" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":20015,"count":1},{"id":21015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="508">
@@ -11117,10 +10105,8 @@
       <c r="D508" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E508" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":11015,"count":1},{"id":12015,"count":1}]}</t>
-        </is>
+      <c r="E508" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":11015,"count":1},{"id":12015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="509">
@@ -11138,10 +10124,8 @@
       <c r="D509" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E509" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":13015,"count":1},{"id":14015,"count":1}]}</t>
-        </is>
+      <c r="E509" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":13015,"count":1},{"id":14015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="510">
@@ -11159,10 +10143,8 @@
       <c r="D510" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E510" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":15015,"count":1},{"id":16015,"count":1}]}</t>
-        </is>
+      <c r="E510" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":15015,"count":1},{"id":16015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="511">
@@ -11180,10 +10162,8 @@
       <c r="D511" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E511" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":23015,"count":1},{"id":24015,"count":1}]}</t>
-        </is>
+      <c r="E511" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":23015,"count":1},{"id":24015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="512">
@@ -11201,10 +10181,8 @@
       <c r="D512" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E512" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":17015,"count":1},{"id":18015,"count":1}]}</t>
-        </is>
+      <c r="E512" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":17015,"count":1},{"id":18015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="513">
@@ -11222,10 +10200,8 @@
       <c r="D513" s="3" t="n">
         <v>10731385</v>
       </c>
-      <c r="E513" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":19015,"count":1},{"id":20015,"count":1}]}</t>
-        </is>
+      <c r="E513" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":19015,"count":1},{"id":20015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="514">
@@ -11243,10 +10219,8 @@
       <c r="D514" s="3" t="n">
         <v>10731385</v>
       </c>
-      <c r="E514" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":15}],"items":[{"id":21015,"count":1},{"id":11015,"count":1}]}</t>
-        </is>
+      <c r="E514" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":15}],"items":[{"id":21015,"count":1},{"id":11015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="515">
@@ -11264,10 +10238,8 @@
       <c r="D515" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E515" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":12015,"count":1},{"id":13015,"count":1}]}</t>
-        </is>
+      <c r="E515" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":12015,"count":1},{"id":13015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="516">
@@ -11285,10 +10257,8 @@
       <c r="D516" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E516" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":14015,"count":1},{"id":15015,"count":1}]}</t>
-        </is>
+      <c r="E516" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":14015,"count":1},{"id":15015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="517">
@@ -11306,10 +10276,8 @@
       <c r="D517" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E517" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":16015,"count":1},{"id":23015,"count":1}]}</t>
-        </is>
+      <c r="E517" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":16015,"count":1},{"id":23015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="518">
@@ -11327,10 +10295,8 @@
       <c r="D518" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E518" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":24015,"count":1},{"id":17015,"count":1}]}</t>
-        </is>
+      <c r="E518" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":24015,"count":1},{"id":17015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="519">
@@ -11348,10 +10314,8 @@
       <c r="D519" s="3" t="n">
         <v>10731385</v>
       </c>
-      <c r="E519" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":18015,"count":1},{"id":19015,"count":1}]}</t>
-        </is>
+      <c r="E519" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":18015,"count":1},{"id":19015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="520">
@@ -11369,10 +10333,8 @@
       <c r="D520" s="3" t="n">
         <v>10731385</v>
       </c>
-      <c r="E520" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":20015,"count":1},{"id":21015,"count":1}]}</t>
-        </is>
+      <c r="E520" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":20015,"count":1},{"id":21015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="521">
@@ -11390,10 +10352,8 @@
       <c r="D521" s="3" t="n">
         <v>10731385</v>
       </c>
-      <c r="E521" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":11015,"count":1},{"id":12015,"count":1}]}</t>
-        </is>
+      <c r="E521" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":11015,"count":1},{"id":12015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="522">
@@ -11411,10 +10371,8 @@
       <c r="D522" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E522" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":15}],"items":[{"id":13015,"count":1},{"id":14015,"count":1}]}</t>
-        </is>
+      <c r="E522" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":15}],"items":[{"id":13015,"count":1},{"id":14015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="523">
@@ -11432,10 +10390,8 @@
       <c r="D523" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E523" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":15015,"count":1},{"id":16015,"count":1}]}</t>
-        </is>
+      <c r="E523" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":15015,"count":1},{"id":16015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="524">
@@ -11453,10 +10409,8 @@
       <c r="D524" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E524" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":23015,"count":1},{"id":24015,"count":1}]}</t>
-        </is>
+      <c r="E524" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":23015,"count":1},{"id":24015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="525">
@@ -11474,10 +10428,8 @@
       <c r="D525" s="3" t="n">
         <v>10731385</v>
       </c>
-      <c r="E525" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":17015,"count":1},{"id":18015,"count":1}]}</t>
-        </is>
+      <c r="E525" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":17015,"count":1},{"id":18015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="526">
@@ -11495,10 +10447,8 @@
       <c r="D526" s="3" t="n">
         <v>10731385</v>
       </c>
-      <c r="E526" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":19015,"count":1},{"id":20015,"count":1}]}</t>
-        </is>
+      <c r="E526" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":19015,"count":1},{"id":20015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="527">
@@ -11516,10 +10466,8 @@
       <c r="D527" s="3" t="n">
         <v>10731385</v>
       </c>
-      <c r="E527" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":21015,"count":1},{"id":11015,"count":1}]}</t>
-        </is>
+      <c r="E527" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":21015,"count":1},{"id":11015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="528">
@@ -11537,10 +10485,8 @@
       <c r="D528" s="3" t="n">
         <v>10731385</v>
       </c>
-      <c r="E528" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":12015,"count":1},{"id":13015,"count":1}]}</t>
-        </is>
+      <c r="E528" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":12015,"count":1},{"id":13015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="529">
@@ -11558,10 +10504,8 @@
       <c r="D529" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E529" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":14015,"count":1},{"id":15015,"count":1}]}</t>
-        </is>
+      <c r="E529" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":14015,"count":1},{"id":15015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="530">
@@ -11579,10 +10523,8 @@
       <c r="D530" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E530" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":15}],"items":[{"id":16015,"count":1},{"id":23015,"count":1}]}</t>
-        </is>
+      <c r="E530" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":15}],"items":[{"id":16015,"count":1},{"id":23015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="531">
@@ -11600,10 +10542,8 @@
       <c r="D531" s="3" t="n">
         <v>10731385</v>
       </c>
-      <c r="E531" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":24015,"count":1},{"id":17015,"count":1}]}</t>
-        </is>
+      <c r="E531" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":24015,"count":1},{"id":17015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="532">
@@ -11621,10 +10561,8 @@
       <c r="D532" s="3" t="n">
         <v>10731385</v>
       </c>
-      <c r="E532" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":18015,"count":1},{"id":19015,"count":1}]}</t>
-        </is>
+      <c r="E532" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":18015,"count":1},{"id":19015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="533">
@@ -11642,10 +10580,8 @@
       <c r="D533" s="3" t="n">
         <v>10731385</v>
       </c>
-      <c r="E533" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":20015,"count":1},{"id":21015,"count":1}]}</t>
-        </is>
+      <c r="E533" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":20015,"count":1},{"id":21015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="534">
@@ -11663,10 +10599,8 @@
       <c r="D534" s="3" t="n">
         <v>10731385</v>
       </c>
-      <c r="E534" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":11015,"count":1},{"id":12015,"count":1}]}</t>
-        </is>
+      <c r="E534" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":11015,"count":1},{"id":12015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="535">
@@ -11684,10 +10618,8 @@
       <c r="D535" s="3" t="n">
         <v>10731385</v>
       </c>
-      <c r="E535" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":13015,"count":1},{"id":14015,"count":1}]}</t>
-        </is>
+      <c r="E535" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":13015,"count":1},{"id":14015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="536">
@@ -11705,10 +10637,8 @@
       <c r="D536" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E536" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":15015,"count":1},{"id":16015,"count":1}]}</t>
-        </is>
+      <c r="E536" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":15015,"count":1},{"id":16015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="537">
@@ -11726,10 +10656,8 @@
       <c r="D537" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E537" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":23015,"count":1},{"id":24015,"count":1}]}</t>
-        </is>
+      <c r="E537" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":23015,"count":1},{"id":24015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="538">
@@ -11747,10 +10675,8 @@
       <c r="D538" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E538" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":15}],"items":[{"id":17015,"count":1},{"id":18015,"count":1}]}</t>
-        </is>
+      <c r="E538" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":15}],"items":[{"id":17015,"count":1},{"id":18015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="539">
@@ -11768,10 +10694,8 @@
       <c r="D539" s="3" t="n">
         <v>12877662</v>
       </c>
-      <c r="E539" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":19015,"count":1},{"id":20015,"count":1}]}</t>
-        </is>
+      <c r="E539" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":19015,"count":1},{"id":20015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="540">
@@ -11789,10 +10713,8 @@
       <c r="D540" s="3" t="n">
         <v>12877662</v>
       </c>
-      <c r="E540" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":21015,"count":1},{"id":11015,"count":1}]}</t>
-        </is>
+      <c r="E540" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":21015,"count":1},{"id":11015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="541">
@@ -11810,10 +10732,8 @@
       <c r="D541" s="3" t="n">
         <v>12877662</v>
       </c>
-      <c r="E541" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":12015,"count":1},{"id":13015,"count":1}]}</t>
-        </is>
+      <c r="E541" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":12015,"count":1},{"id":13015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="542">
@@ -11831,10 +10751,8 @@
       <c r="D542" s="3" t="n">
         <v>12877662</v>
       </c>
-      <c r="E542" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":14015,"count":1},{"id":15015,"count":1}]}</t>
-        </is>
+      <c r="E542" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":14015,"count":1},{"id":15015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="543">
@@ -11852,10 +10770,8 @@
       <c r="D543" s="3" t="n">
         <v>12877662</v>
       </c>
-      <c r="E543" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":16015,"count":1},{"id":23015,"count":1}]}</t>
-        </is>
+      <c r="E543" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":16015,"count":1},{"id":23015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="544">
@@ -11873,10 +10789,8 @@
       <c r="D544" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E544" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":24015,"count":1},{"id":17015,"count":1}]}</t>
-        </is>
+      <c r="E544" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":24015,"count":1},{"id":17015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="545">
@@ -11894,10 +10808,8 @@
       <c r="D545" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E545" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":18015,"count":1},{"id":19015,"count":1}]}</t>
-        </is>
+      <c r="E545" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":18015,"count":1},{"id":19015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="546">
@@ -11915,10 +10827,8 @@
       <c r="D546" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E546" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":15}],"items":[{"id":20015,"count":1},{"id":21015,"count":1}]}</t>
-        </is>
+      <c r="E546" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":15}],"items":[{"id":20015,"count":1},{"id":21015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="547">
@@ -11936,10 +10846,8 @@
       <c r="D547" s="3" t="n">
         <v>12877662</v>
       </c>
-      <c r="E547" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":11015,"count":1},{"id":12015,"count":1}]}</t>
-        </is>
+      <c r="E547" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":11015,"count":1},{"id":12015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="548">
@@ -11957,10 +10865,8 @@
       <c r="D548" s="3" t="n">
         <v>12877662</v>
       </c>
-      <c r="E548" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":13015,"count":1},{"id":14015,"count":1}]}</t>
-        </is>
+      <c r="E548" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":13015,"count":1},{"id":14015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="549">
@@ -11978,10 +10884,8 @@
       <c r="D549" s="3" t="n">
         <v>12877662</v>
       </c>
-      <c r="E549" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":15015,"count":1},{"id":16015,"count":1}]}</t>
-        </is>
+      <c r="E549" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":15015,"count":1},{"id":16015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="550">
@@ -11999,10 +10903,8 @@
       <c r="D550" s="3" t="n">
         <v>12877662</v>
       </c>
-      <c r="E550" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":23015,"count":1},{"id":24015,"count":1}]}</t>
-        </is>
+      <c r="E550" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":23015,"count":1},{"id":24015,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="551">
@@ -12020,10 +10922,8 @@
       <c r="D551" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E551" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":17015,"count":1},{"id":18016,"count":1}]}</t>
-        </is>
+      <c r="E551" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":17015,"count":1},{"id":18016,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="552">
@@ -12041,10 +10941,8 @@
       <c r="D552" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E552" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":19016,"count":1},{"id":20016,"count":1}]}</t>
-        </is>
+      <c r="E552" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":19016,"count":1},{"id":20016,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="553">
@@ -12062,10 +10960,8 @@
       <c r="D553" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E553" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":21016,"count":1},{"id":11016,"count":1}]}</t>
-        </is>
+      <c r="E553" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":21016,"count":1},{"id":11016,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="554">
@@ -12083,10 +10979,8 @@
       <c r="D554" s="3" t="n">
         <v>11706966</v>
       </c>
-      <c r="E554" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":15}],"items":[{"id":12016,"count":1},{"id":13016,"count":1}]}</t>
-        </is>
+      <c r="E554" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":15}],"items":[{"id":12016,"count":1},{"id":13016,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="555">
@@ -12104,10 +10998,8 @@
       <c r="D555" s="3" t="n">
         <v>12877662</v>
       </c>
-      <c r="E555" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":14016,"count":1},{"id":15016,"count":1}]}</t>
-        </is>
+      <c r="E555" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":14016,"count":1},{"id":15016,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="556">
@@ -12125,10 +11017,8 @@
       <c r="D556" s="3" t="n">
         <v>12877662</v>
       </c>
-      <c r="E556" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":16016,"count":1},{"id":23016,"count":1}]}</t>
-        </is>
+      <c r="E556" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587301},{"token":3,"amount":16}],"items":[{"id":16016,"count":1},{"id":23016,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
     <row r="557">
@@ -12146,10 +11036,8 @@
       <c r="D557" s="3" t="n">
         <v>12877662</v>
       </c>
-      <c r="E557" s="3" t="inlineStr">
-        <is>
-          <t>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":24016,"count":1},{"id":17016,"count":1}]}</t>
-        </is>
+      <c r="E557" t="str" s="3">
+        <v>{"tokens":[{"token":4,"amount":1587302},{"token":3,"amount":16}],"items":[{"id":24016,"count":1},{"id":17016,"count":1},{"id":1704,"count":1}]}</v>
       </c>
     </row>
   </sheetData>
